--- a/BONDchart/forecast.xlsx
+++ b/BONDchart/forecast.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,7 +518,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>MISS — closed 98.55, above the 98.45 high. Two causes: (1) data revision — Fri 07-24 actually closed 98.20, not the 97.66 the forecast was anchored to, so the anchor itself was 0.54 too low; (2) underestimated the ceasefire relief trade — 'neutral, slight drift down' was wrong-way vs a +1.4% two-day rebound. Lesson: verify the anchor close against final revised data before forecasting, and weight ceasefire headlines as strongly bullish, not just 'caps the downside'.</t>
+          <t>Initially judged MISS mid-week (Mon close 98.55 &gt; 98.45 high, on revised 07-24 data — anchor was 0.54 too low). Hawkish Jul 29 FOMC then knocked price back to 97.93, inside the 97.00-98.45 range: provisional HIT as of Wed 07-29; final verdict at Friday's close. Lessons stand: verify the anchor against revised data, and don't call a HIT/MISS before the week completes.</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,11 @@
       <c r="I6" t="n">
         <v>98.55</v>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>superseded by 2026-07-29 re-anchor (drift -0.62, hawkish FOMC)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -722,7 +726,11 @@
       <c r="I7" t="n">
         <v>98.55</v>
       </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>superseded by 2026-07-29 re-anchor (drift -0.62, hawkish FOMC)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -760,7 +768,11 @@
       <c r="I8" t="n">
         <v>98.55</v>
       </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>superseded by 2026-07-29 re-anchor (drift -0.62, hawkish FOMC)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -798,7 +810,163 @@
       <c r="I9" t="n">
         <v>98.55</v>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>superseded by 2026-07-29 re-anchor (drift -0.62, hawkish FOMC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>97.93000000000001</v>
+      </c>
+      <c r="C10" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>🇮🇷</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 1 — Ceasefire decision week, post-FOMC reset&lt;/b&gt;&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; base case — the 10-day truce is signed and Hormuz risk premium keeps bleeding out of oil.&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; hawkish Jul 29 hold caps the upside — the old 99.40 target is off the table; relief now tops out near 98.90.&lt;br&gt;&lt;i&gt;Bias: modestly bullish — truce relief vs. hawkish-Fed drag.&lt;/i&gt;</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>97.93000000000001</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="C11" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="E11" t="n">
+        <v>98</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>🇺🇸</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 2 — Truce credibility tested, US CPI lands&lt;/b&gt;&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; every ceasefire this year (8 Apr, 19 Jun) broke within weeks — a 10-day truce expires fast.&lt;br&gt;🇺🇸 &lt;b&gt;US inflation:&lt;/b&gt; July CPI is the swing factor — with the Fed already flagging oil pass-through, a hot print revives hike pricing.&lt;br&gt;&lt;i&gt;Bias: fade the bounce below 99.40 resistance.&lt;/i&gt;</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>97.93000000000001</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>98</v>
+      </c>
+      <c r="C12" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="E12" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>🇪🇺</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 3 — Fade into the September central-bank gauntlet&lt;/b&gt;&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; truce lapses or frays; Houthi blockade threat on Saudi opens a second front.&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; markets price the 10 Sept projection meeting, where another hike is live — and the Fed is already hawkish.&lt;br&gt;&lt;i&gt;Bias: bearish — back below the 98.02 pivot.&lt;/i&gt;</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>97.93000000000001</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="C13" t="n">
+        <v>98</v>
+      </c>
+      <c r="D13" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="E13" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>🇺🇸</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 4 — Jackson Hole&lt;/b&gt;&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; Powell at Jackson Hole ahead of the 15-16 Sept FOMC — after the hawkish July statement, oil-inflation framing there can reset the whole curve.&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; Sept-hike pricing firms in sympathy.&lt;br&gt;&lt;i&gt;Bias: bearish — test of the 96.60 YTD low. Watch: Hormuz transits, Brent above $95.&lt;/i&gt;</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>97.93000000000001</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BONDchart/forecast.xlsx
+++ b/BONDchart/forecast.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,10 +485,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
+      <c r="A2" s="2" t="n">
+        <v>46234</v>
       </c>
       <c r="B2" t="n">
         <v>97.66</v>
@@ -508,25 +510,21 @@
           <t>&lt;b&gt;Week 1 — FOMC week (Jul 28-29)&lt;/b&gt;&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; hold is priced, but hawkish oil-inflation language would push Treasury yields up and drag BTP with them.&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; post-hold digestion; Lagarde's hawkish-leaning tone caps rallies.&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; the mooted 10-day ceasefire caps the downside.&lt;br&gt;&lt;i&gt;Bias: neutral, slight downward drift — chop around the broken 97.37 level.&lt;/i&gt;</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
+      <c r="H2" s="2" t="n">
+        <v>46227</v>
       </c>
       <c r="I2" t="n">
         <v>97.66</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Initially judged MISS mid-week (Mon close 98.55 &gt; 98.45 high, on revised 07-24 data — anchor was 0.54 too low). Hawkish Jul 29 FOMC then knocked price back to 97.93, inside the 97.00-98.45 range: provisional HIT as of Wed 07-29; final verdict at Friday's close. Lessons stand: verify the anchor against revised data, and don't call a HIT/MISS before the week completes.</t>
+          <t>FINAL: HIT — Friday close 97.18 inside 97.00-98.45, red candle as forecast. Mid-week saga: looked like a MISS on Monday (98.55 above the 98.45 high, on revised data), came back in range after the hawkish Jul 29 FOMC. Lessons kept: verify the anchor against revised data; never call HIT/MISS before the week completes.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
+      <c r="A3" s="2" t="n">
+        <v>46241</v>
       </c>
       <c r="B3" t="n">
         <v>97.45</v>
@@ -550,10 +548,8 @@
           <t>&lt;b&gt;Week 2 — Relief bounce IF the ceasefire lands&lt;/b&gt; (see 2026-07-27 vintage)</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
+      <c r="H3" s="2" t="n">
+        <v>46227</v>
       </c>
       <c r="I3" t="n">
         <v>97.66</v>
@@ -565,10 +561,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
+      <c r="A4" s="2" t="n">
+        <v>46248</v>
       </c>
       <c r="B4" t="n">
         <v>98.25</v>
@@ -592,10 +586,8 @@
           <t>&lt;b&gt;Week 3 — Truce credibility tested, US CPI lands&lt;/b&gt; (see 2026-07-27 vintage)</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
+      <c r="H4" s="2" t="n">
+        <v>46227</v>
       </c>
       <c r="I4" t="n">
         <v>97.66</v>
@@ -607,10 +599,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
+      <c r="A5" s="2" t="n">
+        <v>46255</v>
       </c>
       <c r="B5" t="n">
         <v>97.75</v>
@@ -634,10 +624,8 @@
           <t>&lt;b&gt;Week 4 — Renewed downside into the September central-bank gauntlet&lt;/b&gt; (see 2026-07-27 vintage)</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
+      <c r="H5" s="2" t="n">
+        <v>46227</v>
       </c>
       <c r="I5" t="n">
         <v>97.66</v>
@@ -649,10 +637,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
+      <c r="A6" s="2" t="n">
+        <v>46241</v>
       </c>
       <c r="B6" t="n">
         <v>98.55</v>
@@ -676,10 +662,8 @@
           <t>&lt;b&gt;Week 1 — Ceasefire lands, FOMC digested&lt;/b&gt;&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; base case — the 10-day truce is accepted, Hormuz partially normalizes, oil drops further.&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; post-FOMC drift; falling oil lets cut bets creep back into the Treasury curve — tailwind for a test of the 99.40 level.&lt;br&gt;⚠️ &lt;b&gt;US politics:&lt;/b&gt; Trump's retaliation pledge could still kill the deal.&lt;br&gt;&lt;i&gt;Bias: bullish — momentum from the two-day +1.4% rebound carries.&lt;/i&gt;</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
+      <c r="H6" s="2" t="n">
+        <v>46230</v>
       </c>
       <c r="I6" t="n">
         <v>98.55</v>
@@ -691,10 +675,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
+      <c r="A7" s="2" t="n">
+        <v>46248</v>
       </c>
       <c r="B7" t="n">
         <v>99.09999999999999</v>
@@ -718,10 +700,8 @@
           <t>&lt;b&gt;Week 2 — Truce credibility tested, US CPI lands&lt;/b&gt;&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; every ceasefire this year (8 Apr, 19 Jun) broke within weeks — a 10-day truce expires fast.&lt;br&gt;🇺🇸 &lt;b&gt;US inflation:&lt;/b&gt; July CPI (mid-Aug) is the swing factor — an oil-driven hot print revives Fed-hike pricing.&lt;br&gt;&lt;i&gt;Bias: fade the rally at 99.40 resistance. Pattern: repeated truce-break cycles YTD.&lt;/i&gt;</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
+      <c r="H7" s="2" t="n">
+        <v>46230</v>
       </c>
       <c r="I7" t="n">
         <v>98.55</v>
@@ -733,10 +713,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
+      <c r="A8" s="2" t="n">
+        <v>46255</v>
       </c>
       <c r="B8" t="n">
         <v>98.5</v>
@@ -760,10 +738,8 @@
           <t>&lt;b&gt;Week 3 — Fade into the September central-bank gauntlet&lt;/b&gt;&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; truce lapses or frays; Houthi blockade threat on Saudi opens a second front.&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; markets start pricing the 10 Sept projection meeting, where another hike is live.&lt;br&gt;&lt;i&gt;Bias: bearish — back below the 98.36 pivot.&lt;/i&gt;</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
+      <c r="H8" s="2" t="n">
+        <v>46230</v>
       </c>
       <c r="I8" t="n">
         <v>98.55</v>
@@ -775,10 +751,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
+      <c r="A9" s="2" t="n">
+        <v>46262</v>
       </c>
       <c r="B9" t="n">
         <v>97.7</v>
@@ -802,10 +776,8 @@
           <t>&lt;b&gt;Week 4 — Jackson Hole&lt;/b&gt;&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; Powell at Jackson Hole (late Aug) ahead of the 15-16 Sept FOMC — hawkish oil-inflation framing is the risk that resets the curve.&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; Sept-hike pricing firms in sympathy.&lt;br&gt;&lt;i&gt;Bias: bearish — drift toward the 96.60 YTD low. Watch: Hormuz transits, Brent above $95.&lt;/i&gt;</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
+      <c r="H9" s="2" t="n">
+        <v>46230</v>
       </c>
       <c r="I9" t="n">
         <v>98.55</v>
@@ -817,10 +789,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
+      <c r="A10" s="2" t="n">
+        <v>46241</v>
       </c>
       <c r="B10" t="n">
         <v>97.93000000000001</v>
@@ -844,21 +814,21 @@
           <t>&lt;b&gt;Week 1 — Ceasefire decision week, post-FOMC reset&lt;/b&gt;&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; base case — the 10-day truce is signed and Hormuz risk premium keeps bleeding out of oil.&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; hawkish Jul 29 hold caps the upside — the old 99.40 target is off the table; relief now tops out near 98.90.&lt;br&gt;&lt;i&gt;Bias: modestly bullish — truce relief vs. hawkish-Fed drag.&lt;/i&gt;</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
+      <c r="H10" s="2" t="n">
+        <v>46232</v>
       </c>
       <c r="I10" t="n">
         <v>97.93000000000001</v>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>superseded by 2026-07-31 re-anchor (drift -0.75, post-FOMC selloff extended, 97.33 support broken)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
+      <c r="A11" s="2" t="n">
+        <v>46248</v>
       </c>
       <c r="B11" t="n">
         <v>98.59999999999999</v>
@@ -882,21 +852,21 @@
           <t>&lt;b&gt;Week 2 — Truce credibility tested, US CPI lands&lt;/b&gt;&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; every ceasefire this year (8 Apr, 19 Jun) broke within weeks — a 10-day truce expires fast.&lt;br&gt;🇺🇸 &lt;b&gt;US inflation:&lt;/b&gt; July CPI is the swing factor — with the Fed already flagging oil pass-through, a hot print revives hike pricing.&lt;br&gt;&lt;i&gt;Bias: fade the bounce below 99.40 resistance.&lt;/i&gt;</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
+      <c r="H11" s="2" t="n">
+        <v>46232</v>
       </c>
       <c r="I11" t="n">
         <v>97.93000000000001</v>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>superseded by 2026-07-31 re-anchor (drift -0.75, post-FOMC selloff extended, 97.33 support broken)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
+      <c r="A12" s="2" t="n">
+        <v>46255</v>
       </c>
       <c r="B12" t="n">
         <v>98</v>
@@ -920,21 +890,21 @@
           <t>&lt;b&gt;Week 3 — Fade into the September central-bank gauntlet&lt;/b&gt;&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; truce lapses or frays; Houthi blockade threat on Saudi opens a second front.&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; markets price the 10 Sept projection meeting, where another hike is live — and the Fed is already hawkish.&lt;br&gt;&lt;i&gt;Bias: bearish — back below the 98.02 pivot.&lt;/i&gt;</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
+      <c r="H12" s="2" t="n">
+        <v>46232</v>
       </c>
       <c r="I12" t="n">
         <v>97.93000000000001</v>
       </c>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>superseded by 2026-07-31 re-anchor (drift -0.75, post-FOMC selloff extended, 97.33 support broken)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
+      <c r="A13" s="2" t="n">
+        <v>46262</v>
       </c>
       <c r="B13" t="n">
         <v>97.3</v>
@@ -958,15 +928,153 @@
           <t>&lt;b&gt;Week 4 — Jackson Hole&lt;/b&gt;&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; Powell at Jackson Hole ahead of the 15-16 Sept FOMC — after the hawkish July statement, oil-inflation framing there can reset the whole curve.&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; Sept-hike pricing firms in sympathy.&lt;br&gt;&lt;i&gt;Bias: bearish — test of the 96.60 YTD low. Watch: Hormuz transits, Brent above $95.&lt;/i&gt;</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
+      <c r="H13" s="2" t="n">
+        <v>46232</v>
       </c>
       <c r="I13" t="n">
         <v>97.93000000000001</v>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>superseded by 2026-07-31 re-anchor (drift -0.75, post-FOMC selloff extended, 97.33 support broken)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97.18000000000001</v>
+      </c>
+      <c r="C14" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="E14" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>🇮🇷</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 1 — Ceasefire decision week, oversold bounce&lt;/b&gt;&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; base case — the 10-day truce finally gets signed; oil's risk premium bleeds out and BTP reclaims the broken 97.33 level.&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; the hawkish Jul 29 hold caps any relief well below the 98.36 pivot.&lt;br&gt;&lt;i&gt;Bias: modest relief bounce — but rallies are for selling now.&lt;/i&gt;</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="I14" t="n">
+        <v>97.18000000000001</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="C15" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="E15" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>🇺🇸</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 2 — Truce credibility tested, US CPI lands&lt;/b&gt;&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; every ceasefire this year (8 Apr, 19 Jun) broke within weeks — a 10-day truce expires fast.&lt;br&gt;🇺🇸 &lt;b&gt;US inflation:&lt;/b&gt; July CPI is the swing factor — with the Fed already flagging oil pass-through, a hot print revives hike pricing.&lt;br&gt;&lt;i&gt;Bias: fade the bounce below 98.36 resistance; back to the 97.33 line.&lt;/i&gt;</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="I15" t="n">
+        <v>97.18000000000001</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="D16" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>🇪🇺</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 3 — Fade into the September central-bank gauntlet&lt;/b&gt;&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; the truce lapses or frays; Houthi blockade threat on Saudi opens a second front.&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; markets price the 10 Sept projection meeting, where another hike is live — and the Fed is already hawkish.&lt;br&gt;&lt;i&gt;Bias: bearish — 97.33 gives way again, first test of the 96.60 YTD low.&lt;/i&gt;</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="I16" t="n">
+        <v>97.18000000000001</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B17" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="C17" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="E17" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>🇺🇸</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 4 — Jackson Hole&lt;/b&gt;&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; Powell at Jackson Hole ahead of the 15-16 Sept FOMC — after the hawkish July statement, oil-inflation framing there can crack the floor.&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; Sept-hike pricing firms in sympathy.&lt;br&gt;&lt;i&gt;Bias: bearish — break of the 96.60 YTD low toward 95.90. Watch: Hormuz transits, Brent above $95.&lt;/i&gt;</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="I17" t="n">
+        <v>97.18000000000001</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BONDchart/forecast.xlsx
+++ b/BONDchart/forecast.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -972,7 +972,11 @@
       <c r="I14" t="n">
         <v>97.18000000000001</v>
       </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>PROVISIONAL MISS (judged Wed 08-05, close 98.90 vs fc high 98.10 — final verdict at Friday close, remember the 07-31 flip-flop). Post-mortem: direction RIGHT (truce bounce) but magnitude badly wrong — capped the rally at 98.10 believing the hawkish Fed would hold it under 98.36; the signed ceasefire (Aug 2) blew through both by Tuesday. Lesson 1: after a capitulation week that breaks support, relief rallies overshoot — don't cap the bounce at the nearest resistance. Lesson 2: the 'bolder call' (break of 96.60) was made AT the local low = recency bias; boldness belongs mid-trend, not at extremes.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1006,7 +1010,11 @@
       <c r="I15" t="n">
         <v>97.18000000000001</v>
       </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>superseded by 2026-08-05 re-anchor (drift +1.72, ceasefire signed Aug 2, rally through 98.36)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1040,7 +1048,11 @@
       <c r="I16" t="n">
         <v>97.18000000000001</v>
       </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>superseded by 2026-08-05 re-anchor (drift +1.72, ceasefire signed Aug 2, rally through 98.36)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1074,7 +1086,147 @@
       <c r="I17" t="n">
         <v>97.18000000000001</v>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>superseded by 2026-08-05 re-anchor (drift +1.72, ceasefire signed Aug 2, rally through 98.36)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="C18" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>99.05</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>🇺🇸</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 1 — Truce rally meets US CPI&lt;/b&gt;&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; the signed truce holds through its first week; oil premium keeps bleeding.&lt;br&gt;🇺🇸 &lt;b&gt;US inflation:&lt;/b&gt; July CPI is the test — oil pass-through was the Fed's stated worry, and the first soft print unlocks more upside.&lt;br&gt;&lt;i&gt;Bias: momentum carries, but the 99.40 resistance caps the first attempt.&lt;/i&gt;</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="I18" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99.05</v>
+      </c>
+      <c r="C19" t="n">
+        <v>99.45</v>
+      </c>
+      <c r="D19" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>98.55</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>🇪🇺</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 2 — September gauntlet comes into view&lt;/b&gt;&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; hawks keep the 10 Sept hike live despite cheaper oil — pricing firms as the meeting nears.&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; minutes of the hawkish July FOMC re-read badly.&lt;br&gt;&lt;i&gt;Bias: rally stalls under 99.40, fades toward the 97.96 pivot.&lt;/i&gt;</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="I19" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98.55</v>
+      </c>
+      <c r="C20" t="n">
+        <v>99</v>
+      </c>
+      <c r="D20" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="E20" t="n">
+        <v>98</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>🇺🇸</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 3 — Jackson Hole&lt;/b&gt;&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; Powell at Jackson Hole ahead of the 15-16 Sept FOMC — with the truce holding, he can't lean on oil, but 'higher for longer' framing still bites.&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; truce renewal talks at the 10-day expiry are the tail risk.&lt;br&gt;&lt;i&gt;Bias: drift back to the 97.96 support — no floor-break call this time.&lt;/i&gt;</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="I20" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98</v>
+      </c>
+      <c r="C21" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="D21" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>🇪🇺</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 4 — Run-up to the 10 Sept ECB&lt;/b&gt;&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; decision week looms — a second hike is the base case being priced.&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; August payrolls (Fri) set the tone for the Sept FOMC.&lt;br&gt;&lt;i&gt;Bias: heavy into the event risk; 97.96 tested but holds.&lt;/i&gt;</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="I21" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BONDchart/forecast.xlsx
+++ b/BONDchart/forecast.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1124,7 +1124,11 @@
       <c r="I18" t="n">
         <v>98.90000000000001</v>
       </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>The forecast overestimated the bond's strength, likely due to an overly optimistic view on ECB and Fed policies. For the next forecast, it's crucial to closely monitor geopolitical tensions and their immediate impact on markets.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1158,7 +1162,11 @@
       <c r="I19" t="n">
         <v>98.90000000000001</v>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>superseded by 2026-08-14 re-anchor (week 2026-08-14 missed; anchor drift -1.57; user instruction: "i just got new data, run the whole thing")</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1192,7 +1200,11 @@
       <c r="I20" t="n">
         <v>98.90000000000001</v>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>superseded by 2026-08-14 re-anchor (week 2026-08-14 missed; anchor drift -1.57; user instruction: "i just got new data, run the whole thing")</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1226,7 +1238,299 @@
       <c r="I21" t="n">
         <v>98.90000000000001</v>
       </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>superseded by 2026-08-14 re-anchor (week 2026-08-14 missed; anchor drift -1.57; user instruction: "i just got new data, run the whole thing")</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97.33</v>
+      </c>
+      <c r="C22" t="n">
+        <v>98</v>
+      </c>
+      <c r="D22" t="n">
+        <v>97.33</v>
+      </c>
+      <c r="E22" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>🇺🇸</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 1 — Truce rally stalls&lt;/b&gt;&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; hot CPI keeps hike risk alive, 3.25%+ forecast...&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; 10 Sept meeting looms, 2.25% hike confirmed...&lt;br&gt;⚠️ &lt;b&gt;US politics:&lt;/b&gt; midterm election risks, Powell testifies...</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="I22" t="n">
+        <v>97.33</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>superseded by 2026-08-14 re-anchor (user instruction: "i just got new data, run the whole thing")</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="C23" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="E23" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>🇪🇺</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 2 — ECB hikes, truce relief&lt;/b&gt;&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; 2.25% hike confirmed, 2027+ rate path...&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; hawkish stance, 3.50%+ forecast...&lt;br&gt;⚠️ &lt;b&gt;US politics:&lt;/b&gt; midterm election risks, Powell testifies...</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="I23" t="n">
+        <v>97.33</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>superseded by 2026-08-14 re-anchor (user instruction: "i just got new data, run the whole thing")</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="C24" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="D24" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 3 — Midterm election risk&lt;/b&gt;&lt;br&gt;⚠️ &lt;b&gt;US politics:&lt;/b&gt; midterm election risks, Powell testifies...&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; hawkish stance, 3.50%+ forecast...&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; 2.25% hike confirmed, 2027+ rate path...</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="I24" t="n">
+        <v>97.33</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>superseded by 2026-08-14 re-anchor (user instruction: "i just got new data, run the whole thing")</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="C25" t="n">
+        <v>99</v>
+      </c>
+      <c r="D25" t="n">
+        <v>98.45</v>
+      </c>
+      <c r="E25" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>🇪🇺</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 4 — ECB meeting, ceasefire risk&lt;/b&gt;&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; 10 Sept meeting, 2.25%+ hike likely...&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; hawkish stance, 3.50%+ forecast...&lt;br&gt;⚠️ &lt;b&gt;US politics:&lt;/b&gt; midterm election risks, Powell testifies...&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; ceasefire risk, oil prices stabilize...</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="I25" t="n">
+        <v>97.33</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>superseded by 2026-08-14 re-anchor (user instruction: "i just got new data, run the whole thing")</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97.33</v>
+      </c>
+      <c r="C26" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="E26" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>🇮🇹</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 1 — Truce rally stalls&lt;/b&gt;&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; hot CPI keeps hike risk alive, selloffs target 97.91 support.&lt;br&gt;🇮🇹 &lt;b&gt;Italy:&lt;/b&gt; budget deficit fears pressure BTP as ECB holds rates.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>46248.04166666666</v>
+      </c>
+      <c r="I26" t="n">
+        <v>97.33</v>
+      </c>
+      <c r="J26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="C27" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="E27" t="n">
+        <v>97</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>🇪🇺</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 2 — ECB hawkishness dominates&lt;/b&gt;&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; rate hike speculation intensifies ahead of Sept 10 meeting.&lt;br&gt;⚠️ &lt;b&gt;Global:&lt;/b&gt; Iran escalates tensions, but ceasefire limits volatility.</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>46248.04166666666</v>
+      </c>
+      <c r="I27" t="n">
+        <v>97.33</v>
+      </c>
+      <c r="J27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B28" t="n">
+        <v>97</v>
+      </c>
+      <c r="C28" t="n">
+        <v>98</v>
+      </c>
+      <c r="D28" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="E28" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>🇪🇺</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 3 — ECB meeting fallout&lt;/b&gt;&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; 2.25% rate hike confirmed, BTP crashes to 96.60 ATL.&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; dovish pivot weakens bond rally.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>46248.04166666666</v>
+      </c>
+      <c r="I28" t="n">
+        <v>97.33</v>
+      </c>
+      <c r="J28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B29" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="C29" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>97</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>🇪🇺</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 4 — Volatility ahead of Sept 10&lt;/b&gt;&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; inflation data sparks rate hike speculation.&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; Powell hints at pause, but BTP struggles above 97.91.</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>46248.04166666666</v>
+      </c>
+      <c r="I29" t="n">
+        <v>97.33</v>
+      </c>
+      <c r="J29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BONDchart/forecast.xlsx
+++ b/BONDchart/forecast.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1428,7 +1428,11 @@
       <c r="I26" t="n">
         <v>97.33</v>
       </c>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>PROVISIONAL MISS (week not finished): The forecast missed due to an unexpected escalation in the Israel-Iran conflict, triggering a sharper sell-off than modeled. The war's intensification overwhelmed technical factors, breaking support at 97.91 and driving price below 95.89. Lesson: Geopolitical volatility now dominates over central bank cycles, requiring tighter risk premiums and lower high/low projections in volatile environments.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -1462,7 +1466,11 @@
       <c r="I27" t="n">
         <v>97.33</v>
       </c>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>superseded by 2026-08-18 re-anchor (week 2026-08-21 missed; anchor drift -1.33; user instruction: "i just got new data, run all, because the last predictions you made were too optimistic, the war is getting real bad and price is dropping faster than you expected")</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1496,7 +1504,11 @@
       <c r="I28" t="n">
         <v>97.33</v>
       </c>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>superseded by 2026-08-18 re-anchor (week 2026-08-21 missed; anchor drift -1.33; user instruction: "i just got new data, run all, because the last predictions you made were too optimistic, the war is getting real bad and price is dropping faster than you expected")</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -1530,7 +1542,147 @@
       <c r="I29" t="n">
         <v>97.33</v>
       </c>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>superseded by 2026-08-18 re-anchor (week 2026-08-21 missed; anchor drift -1.33; user instruction: "i just got new data, run all, because the last predictions you made were too optimistic, the war is getting real bad and price is dropping faster than you expected")</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B30" t="n">
+        <v>96</v>
+      </c>
+      <c r="C30" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="D30" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="E30" t="n">
+        <v>95.89</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>🇮🇷</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 1 — Truce rally stalls&lt;/b&gt;&lt;br&gt;🇮🇷 &lt;b&gt;War escalation:&lt;/b&gt; intensified strikes in Hormuz disrupt global supply chains, crushing bond prices...&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; inflation sticks above 3.0% despite ceasefire, keeping rate hike risks alive...</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>46252</v>
+      </c>
+      <c r="I30" t="n">
+        <v>96</v>
+      </c>
+      <c r="J30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B31" t="n">
+        <v>95.89</v>
+      </c>
+      <c r="C31" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>95.89</v>
+      </c>
+      <c r="E31" t="n">
+        <v>96</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 2 — Volatile ceasefire tug-of-war&lt;/b&gt;&lt;br&gt;⚠️ &lt;b&gt;Geopolitical uncertainty:&lt;/b&gt; conflicting ceasefire violations trigger stop-loss selling...&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; signals rate pause but warns of inflation risks, adding volatility...</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>46252</v>
+      </c>
+      <c r="I31" t="n">
+        <v>96</v>
+      </c>
+      <c r="J31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B32" t="n">
+        <v>96</v>
+      </c>
+      <c r="C32" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="D32" t="n">
+        <v>95.89</v>
+      </c>
+      <c r="E32" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>🇪🇺</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 3 — ECB meeting anxiety&lt;/b&gt;&lt;br&gt;🇪🇺 &lt;b&gt;ECB policy:&lt;/b&gt; hints at potential 25-bp hike in September, spooking bond buyers...&lt;br&gt;🇮🇹 &lt;b&gt;Italy:&lt;/b&gt; fiscal deficit fears resurface as market prices fall below 97.00...</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>46252</v>
+      </c>
+      <c r="I32" t="n">
+        <v>96</v>
+      </c>
+      <c r="J32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B33" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="C33" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="D33" t="n">
+        <v>95.89</v>
+      </c>
+      <c r="E33" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>🇪🇺</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 4 — ECB decision day&lt;/b&gt;&lt;br&gt;🇪🇺 &lt;b&gt;Rate decision:&lt;/b&gt; 25-bp hike announced, sending BTP to 95.90 as yields surge...&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; maintains hawkish stance, reinforcing bond market selloff...</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>46252</v>
+      </c>
+      <c r="I33" t="n">
+        <v>96</v>
+      </c>
+      <c r="J33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BONDchart/forecast.xlsx
+++ b/BONDchart/forecast.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,209 +486,209 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46234</v>
+        <v>46269</v>
       </c>
       <c r="B2" t="n">
-        <v>97.66</v>
+        <v>96.34</v>
       </c>
       <c r="C2" t="n">
-        <v>98.45</v>
+        <v>96.34</v>
       </c>
       <c r="D2" t="n">
-        <v>97</v>
+        <v>96.34</v>
       </c>
       <c r="E2" t="n">
-        <v>97.45</v>
+        <v>96.34</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>🇺🇸</t>
+          <t>↔️</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Week 1 — FOMC week (Jul 28-29)&lt;/b&gt;&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; hold is priced, but hawkish oil-inflation language would push Treasury yields up and drag BTP with them.&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; post-hold digestion; Lagarde's hawkish-leaning tone caps rallies.&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; the mooted 10-day ceasefire caps the downside.&lt;br&gt;&lt;i&gt;Bias: neutral, slight downward drift — chop around the broken 97.37 level.&lt;/i&gt;</t>
+          <t>PLACEHOLDER — fresh start, no real forecast written yet. Run `python3 run.py "write a fresh 4-week forecast"` to have the AI replace this with a real one.</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>46227</v>
+        <v>46262</v>
       </c>
       <c r="I2" t="n">
-        <v>97.66</v>
+        <v>96.34</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>FINAL: HIT — Friday close 97.18 inside 97.00-98.45, red candle as forecast. Mid-week saga: looked like a MISS on Monday (98.55 above the 98.45 high, on revised data), came back in range after the hawkish Jul 29 FOMC. Lessons kept: verify the anchor against revised data; never call HIT/MISS before the week completes.</t>
+          <t>superseded by 2026-08-28 re-anchor (user instruction: "write a fresh 4-week forecast grounded in the current macro briefing")</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46241</v>
+        <v>46276</v>
       </c>
       <c r="B3" t="n">
-        <v>97.45</v>
+        <v>96.34</v>
       </c>
       <c r="C3" t="n">
-        <v>98.75</v>
+        <v>96.34</v>
       </c>
       <c r="D3" t="n">
-        <v>96.95</v>
+        <v>96.34</v>
       </c>
       <c r="E3" t="n">
-        <v>98.25</v>
+        <v>96.34</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>🇮🇷</t>
+          <t>↔️</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Week 2 — Relief bounce IF the ceasefire lands&lt;/b&gt; (see 2026-07-27 vintage)</t>
+          <t>PLACEHOLDER — fresh start, no real forecast written yet. Run `python3 run.py "write a fresh 4-week forecast"` to have the AI replace this with a real one.</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>46227</v>
+        <v>46262</v>
       </c>
       <c r="I3" t="n">
-        <v>97.66</v>
+        <v>96.34</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>superseded by 2026-07-27 re-anchor (drift +0.89)</t>
+          <t>superseded by 2026-08-28 re-anchor (user instruction: "write a fresh 4-week forecast grounded in the current macro briefing")</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46248</v>
+        <v>46283</v>
       </c>
       <c r="B4" t="n">
-        <v>98.25</v>
+        <v>96.34</v>
       </c>
       <c r="C4" t="n">
-        <v>99</v>
+        <v>96.34</v>
       </c>
       <c r="D4" t="n">
-        <v>97.34999999999999</v>
+        <v>96.34</v>
       </c>
       <c r="E4" t="n">
-        <v>97.75</v>
+        <v>96.34</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>🇺🇸</t>
+          <t>↔️</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Week 3 — Truce credibility tested, US CPI lands&lt;/b&gt; (see 2026-07-27 vintage)</t>
+          <t>PLACEHOLDER — fresh start, no real forecast written yet. Run `python3 run.py "write a fresh 4-week forecast"` to have the AI replace this with a real one.</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>46227</v>
+        <v>46262</v>
       </c>
       <c r="I4" t="n">
-        <v>97.66</v>
+        <v>96.34</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>superseded by 2026-07-27 re-anchor (drift +0.89)</t>
+          <t>superseded by 2026-08-28 re-anchor (user instruction: "write a fresh 4-week forecast grounded in the current macro briefing")</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46255</v>
+        <v>46290</v>
       </c>
       <c r="B5" t="n">
-        <v>97.75</v>
+        <v>96.34</v>
       </c>
       <c r="C5" t="n">
-        <v>98.34999999999999</v>
+        <v>96.34</v>
       </c>
       <c r="D5" t="n">
-        <v>96.5</v>
+        <v>96.34</v>
       </c>
       <c r="E5" t="n">
-        <v>97</v>
+        <v>96.34</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>🇪🇺</t>
+          <t>↔️</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Week 4 — Renewed downside into the September central-bank gauntlet&lt;/b&gt; (see 2026-07-27 vintage)</t>
+          <t>PLACEHOLDER — fresh start, no real forecast written yet. Run `python3 run.py "write a fresh 4-week forecast"` to have the AI replace this with a real one.</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>46227</v>
+        <v>46262</v>
       </c>
       <c r="I5" t="n">
-        <v>97.66</v>
+        <v>96.34</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>superseded by 2026-07-27 re-anchor (drift +0.89)</t>
+          <t>superseded by 2026-08-28 re-anchor (user instruction: "write a fresh 4-week forecast grounded in the current macro briefing")</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46241</v>
+        <v>46269</v>
       </c>
       <c r="B6" t="n">
-        <v>98.55</v>
+        <v>96.34</v>
       </c>
       <c r="C6" t="n">
-        <v>99.40000000000001</v>
+        <v>96.75</v>
       </c>
       <c r="D6" t="n">
-        <v>97.90000000000001</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>99.09999999999999</v>
+        <v>96.05</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>🇮🇷</t>
+          <t>🇺🇸</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Week 1 — Ceasefire lands, FOMC digested&lt;/b&gt;&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; base case — the 10-day truce is accepted, Hormuz partially normalizes, oil drops further.&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; post-FOMC drift; falling oil lets cut bets creep back into the Treasury curve — tailwind for a test of the 99.40 level.&lt;br&gt;⚠️ &lt;b&gt;US politics:&lt;/b&gt; Trump's retaliation pledge could still kill the deal.&lt;br&gt;&lt;i&gt;Bias: bullish — momentum from the two-day +1.4% rebound carries.&lt;/i&gt;</t>
+          <t>&lt;b&gt;Week 1 — Geopolitical Stress Test&lt;/b&gt;&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; PCE inflation remains sticky at +3.7% YoY, keeping rate hike fears elevated through year-end.&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; Coordination efforts in Hormuz intensify, but high US debt levels limit rate cut expectations.&lt;br&gt;🇮🇹 &lt;b&gt;Italy:&lt;/b&gt; Local market focus is overshadowed by escalating US-Middle East tensions and US-China trade conflicts.</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>46230</v>
+        <v>46262.04166666666</v>
       </c>
       <c r="I6" t="n">
-        <v>98.55</v>
+        <v>96.34</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>superseded by 2026-07-29 re-anchor (drift -0.62, hawkish FOMC)</t>
+          <t>PROVISIONAL MISS (week not finished): The forecast missed because the actual weekly move was significantly more bearish than predicted, breaking through key technical support (95.37 close). The sudden geopolitical shock (US striking Iranian targets) provided a major, unpriced downside catalyst that overwhelmed the technical expectation. Going forward, forecasts must heavily weight high-impact, geopolitical risks as potential primary drivers that can invalidate technical setups.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46248</v>
+        <v>46276</v>
       </c>
       <c r="B7" t="n">
-        <v>99.09999999999999</v>
+        <v>96.05</v>
       </c>
       <c r="C7" t="n">
-        <v>99.65000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="D7" t="n">
-        <v>98.15000000000001</v>
+        <v>95.45</v>
       </c>
       <c r="E7" t="n">
-        <v>98.5</v>
+        <v>95.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -697,74 +697,74 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Week 2 — Truce credibility tested, US CPI lands&lt;/b&gt;&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; every ceasefire this year (8 Apr, 19 Jun) broke within weeks — a 10-day truce expires fast.&lt;br&gt;🇺🇸 &lt;b&gt;US inflation:&lt;/b&gt; July CPI (mid-Aug) is the swing factor — an oil-driven hot print revives Fed-hike pricing.&lt;br&gt;&lt;i&gt;Bias: fade the rally at 99.40 resistance. Pattern: repeated truce-break cycles YTD.&lt;/i&gt;</t>
+          <t>&lt;b&gt;Week 2 — Conflict Escalation Fears&lt;/b&gt;&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; Sustained US conflict risk (Hormuz, sanctions) increases global risk premium, pressuring asset prices.&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; NATO allies commit to freedom of navigation, dampening hopes for an early ECB pivot.&lt;br&gt;🌏 &lt;b&gt;Asia:&lt;/b&gt; US-China sanctions showdown looms, creating structural economic uncertainty for global commodity flows.</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>46230</v>
+        <v>46262.04166666666</v>
       </c>
       <c r="I7" t="n">
-        <v>98.55</v>
+        <v>96.34</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>superseded by 2026-07-29 re-anchor (drift -0.62, hawkish FOMC)</t>
+          <t>superseded by 2026-08-31 re-anchor (week 2026-09-04 missed; anchor drift -0.97)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46255</v>
+        <v>46283</v>
       </c>
       <c r="B8" t="n">
-        <v>98.5</v>
+        <v>95.7</v>
       </c>
       <c r="C8" t="n">
-        <v>99</v>
+        <v>95.95</v>
       </c>
       <c r="D8" t="n">
-        <v>97.3</v>
+        <v>94.75</v>
       </c>
       <c r="E8" t="n">
-        <v>97.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>🇪🇺</t>
+          <t>🇺🇸</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Week 3 — Fade into the September central-bank gauntlet&lt;/b&gt;&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; truce lapses or frays; Houthi blockade threat on Saudi opens a second front.&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; markets start pricing the 10 Sept projection meeting, where another hike is live.&lt;br&gt;&lt;i&gt;Bias: bearish — back below the 98.36 pivot.&lt;/i&gt;</t>
+          <t>&lt;b&gt;Week 3 — US-China Showdown Deepens&lt;/b&gt;&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; Focus shifts to the systemic risk posed by US secondary sanctions impacting China's trade stability.&lt;br&gt;🌏 &lt;b&gt;Asia:&lt;/b&gt; China's rejection of US sanctions demands heightens the geopolitical bomb risk, signaling structural decoupling.&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; Global instability forces bond investors to price in higher risk premiums, overriding rate cut hopes.</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>46230</v>
+        <v>46262.04166666666</v>
       </c>
       <c r="I8" t="n">
-        <v>98.55</v>
+        <v>96.34</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>superseded by 2026-07-29 re-anchor (drift -0.62, hawkish FOMC)</t>
+          <t>superseded by 2026-08-31 re-anchor (week 2026-09-04 missed; anchor drift -0.97)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46262</v>
+        <v>46290</v>
       </c>
       <c r="B9" t="n">
-        <v>97.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>98.40000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="D9" t="n">
-        <v>96.7</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>97.09999999999999</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -773,112 +773,112 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Week 4 — Jackson Hole&lt;/b&gt;&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; Powell at Jackson Hole (late Aug) ahead of the 15-16 Sept FOMC — hawkish oil-inflation framing is the risk that resets the curve.&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; Sept-hike pricing firms in sympathy.&lt;br&gt;&lt;i&gt;Bias: bearish — drift toward the 96.60 YTD low. Watch: Hormuz transits, Brent above $95.&lt;/i&gt;</t>
+          <t>&lt;b&gt;Week 4 — Mixed Signals Amid Uncertainty&lt;/b&gt;&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; US inflation data remains sticky, and geopolitical risks persist, capping any major rally.&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; Coordination efforts continue, but the lack of clarity from the US market keeps rate expectations muted.&lt;br&gt;⚠️ &lt;b&gt;US Politics:&lt;/b&gt; Continued high political volatility (Trump/Bessent actions) keeps the risk barometer elevated, limiting downside momentum but maintaining pressure.</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>46230</v>
+        <v>46262.04166666666</v>
       </c>
       <c r="I9" t="n">
-        <v>98.55</v>
+        <v>96.34</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>superseded by 2026-07-29 re-anchor (drift -0.62, hawkish FOMC)</t>
+          <t>superseded by 2026-08-31 re-anchor (week 2026-09-04 missed; anchor drift -0.97)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46241</v>
+        <v>46276</v>
       </c>
       <c r="B10" t="n">
-        <v>97.93000000000001</v>
+        <v>95.37</v>
       </c>
       <c r="C10" t="n">
-        <v>98.90000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>97.2</v>
+        <v>94.8</v>
       </c>
       <c r="E10" t="n">
-        <v>98.59999999999999</v>
+        <v>95</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>🇮🇷</t>
+          <t>↔️</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Week 1 — Ceasefire decision week, post-FOMC reset&lt;/b&gt;&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; base case — the 10-day truce is signed and Hormuz risk premium keeps bleeding out of oil.&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; hawkish Jul 29 hold caps the upside — the old 99.40 target is off the table; relief now tops out near 98.90.&lt;br&gt;&lt;i&gt;Bias: modestly bullish — truce relief vs. hawkish-Fed drag.&lt;/i&gt;</t>
+          <t>&lt;b&gt;Week 1 — Geopolitical Shock Absorbs&lt;/b&gt;&lt;br&gt;⚠️ &lt;b&gt;US politics:&lt;/b&gt; Escalation in the Strait of Hormuz and spiking oil prices drive immediate risk-off sentiment, pressuring yields lower and bond prices down to 95.00.</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>46232</v>
+        <v>46265</v>
       </c>
       <c r="I10" t="n">
-        <v>97.93000000000001</v>
+        <v>95.37</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>superseded by 2026-07-31 re-anchor (drift -0.75, post-FOMC selloff extended, 97.33 support broken)</t>
+          <t>superseded by 2026-08-31 re-anchor (user instruction: "regenerate the forecast icons")</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46248</v>
+        <v>46283</v>
       </c>
       <c r="B11" t="n">
-        <v>98.59999999999999</v>
+        <v>95</v>
       </c>
       <c r="C11" t="n">
-        <v>99.09999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="D11" t="n">
-        <v>97.59999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="E11" t="n">
-        <v>98</v>
+        <v>94.8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>🇺🇸</t>
+          <t>↔️</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Week 2 — Truce credibility tested, US CPI lands&lt;/b&gt;&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; every ceasefire this year (8 Apr, 19 Jun) broke within weeks — a 10-day truce expires fast.&lt;br&gt;🇺🇸 &lt;b&gt;US inflation:&lt;/b&gt; July CPI is the swing factor — with the Fed already flagging oil pass-through, a hot print revives hike pricing.&lt;br&gt;&lt;i&gt;Bias: fade the bounce below 99.40 resistance.&lt;/i&gt;</t>
+          <t>&lt;b&gt;Week 2 — Oil Price Shock Dominates&lt;/b&gt;&lt;br&gt;⛽ &lt;b&gt;Global Commodity:&lt;/b&gt; Sustained oil price spikes amid regional conflict keep global recession fears high, causing the bond to consolidate near the ATL at 94.80.</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>46232</v>
+        <v>46265</v>
       </c>
       <c r="I11" t="n">
-        <v>97.93000000000001</v>
+        <v>95.37</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>superseded by 2026-07-31 re-anchor (drift -0.75, post-FOMC selloff extended, 97.33 support broken)</t>
+          <t>superseded by 2026-08-31 re-anchor (user instruction: "regenerate the forecast icons")</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46255</v>
+        <v>46290</v>
       </c>
       <c r="B12" t="n">
-        <v>98</v>
+        <v>94.8</v>
       </c>
       <c r="C12" t="n">
-        <v>98.5</v>
+        <v>95.5</v>
       </c>
       <c r="D12" t="n">
-        <v>96.90000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="E12" t="n">
-        <v>97.3</v>
+        <v>95.2</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -887,802 +887,346 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Week 3 — Fade into the September central-bank gauntlet&lt;/b&gt;&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; truce lapses or frays; Houthi blockade threat on Saudi opens a second front.&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; markets price the 10 Sept projection meeting, where another hike is live — and the Fed is already hawkish.&lt;br&gt;&lt;i&gt;Bias: bearish — back below the 98.02 pivot.&lt;/i&gt;</t>
+          <t>&lt;b&gt;Week 3 — ECB Manages Energy Crisis&lt;/b&gt;&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; Central bank rhetoric focuses on energy security and inflation management, providing temporary support and lifting the bond back toward 95.20.</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>46232</v>
+        <v>46265</v>
       </c>
       <c r="I12" t="n">
-        <v>97.93000000000001</v>
+        <v>95.37</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>superseded by 2026-07-31 re-anchor (drift -0.75, post-FOMC selloff extended, 97.33 support broken)</t>
+          <t>superseded by 2026-08-31 re-anchor (user instruction: "regenerate the forecast icons")</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46262</v>
+        <v>46297</v>
       </c>
       <c r="B13" t="n">
-        <v>97.3</v>
+        <v>95.2</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>96.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>96.8</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>🇺🇸</t>
+          <t>🇮🇹</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Week 4 — Jackson Hole&lt;/b&gt;&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; Powell at Jackson Hole ahead of the 15-16 Sept FOMC — after the hawkish July statement, oil-inflation framing there can reset the whole curve.&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; Sept-hike pricing firms in sympathy.&lt;br&gt;&lt;i&gt;Bias: bearish — test of the 96.60 YTD low. Watch: Hormuz transits, Brent above $95.&lt;/i&gt;</t>
+          <t>&lt;b&gt;Week 4 — Sovereign Risk Assessment&lt;/b&gt;&lt;br&gt;🇮🇹 &lt;b&gt;Italy:&lt;/b&gt; Market focuses on the sovereign's ability to absorb global energy shocks, leading to a slight downward drift and testing local support at 95.10.</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>46232</v>
+        <v>46265</v>
       </c>
       <c r="I13" t="n">
-        <v>97.93000000000001</v>
+        <v>95.37</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>superseded by 2026-07-31 re-anchor (drift -0.75, post-FOMC selloff extended, 97.33 support broken)</t>
+          <t>superseded by 2026-08-31 re-anchor (user instruction: "regenerate the forecast icons")</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46241</v>
+        <v>46276</v>
       </c>
       <c r="B14" t="n">
-        <v>97.18000000000001</v>
+        <v>95.37</v>
       </c>
       <c r="C14" t="n">
-        <v>98.09999999999999</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>96.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="E14" t="n">
-        <v>97.8</v>
+        <v>95.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>🇮🇷</t>
+          <t>💥</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Week 1 — Ceasefire decision week, oversold bounce&lt;/b&gt;&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; base case — the 10-day truce finally gets signed; oil's risk premium bleeds out and BTP reclaims the broken 97.33 level.&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; the hawkish Jul 29 hold caps any relief well below the 98.36 pivot.&lt;br&gt;&lt;i&gt;Bias: modest relief bounce — but rallies are for selling now.&lt;/i&gt;</t>
+          <t>&lt;b&gt;Week 1 — Initial Shock Absorption&lt;/b&gt;&lt;br&gt;💥 &lt;b&gt;War:&lt;/b&gt; US striking Iranian targets spikes oil prices and triggers immediate sell-off pressure on Italian debt, testing immediate support.&lt;br&gt;🇮🇹 &lt;b&gt;Italy:&lt;/b&gt; BTPs react sharply to the geopolitical shock, consolidating near the ATL 95.30 level.</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>46234</v>
+        <v>46265.04166666666</v>
       </c>
       <c r="I14" t="n">
-        <v>97.18000000000001</v>
+        <v>95.37</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>PROVISIONAL MISS (judged Wed 08-05, close 98.90 vs fc high 98.10 — final verdict at Friday close, remember the 07-31 flip-flop). Post-mortem: direction RIGHT (truce bounce) but magnitude badly wrong — capped the rally at 98.10 believing the hawkish Fed would hold it under 98.36; the signed ceasefire (Aug 2) blew through both by Tuesday. Lesson 1: after a capitulation week that breaks support, relief rallies overshoot — don't cap the bounce at the nearest resistance. Lesson 2: the 'bolder call' (break of 96.60) was made AT the local low = recency bias; boldness belongs mid-trend, not at extremes.</t>
+          <t>superseded by 2026-08-31 re-anchor (user instruction: "run it again, got fresh data, focus on Iran war and FED expectations")</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46248</v>
+        <v>46283</v>
       </c>
       <c r="B15" t="n">
-        <v>97.8</v>
+        <v>95.5</v>
       </c>
       <c r="C15" t="n">
-        <v>98.3</v>
+        <v>95.7</v>
       </c>
       <c r="D15" t="n">
-        <v>96.90000000000001</v>
+        <v>95.25</v>
       </c>
       <c r="E15" t="n">
-        <v>97.3</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>🇺🇸</t>
+          <t>💥</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Week 2 — Truce credibility tested, US CPI lands&lt;/b&gt;&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; every ceasefire this year (8 Apr, 19 Jun) broke within weeks — a 10-day truce expires fast.&lt;br&gt;🇺🇸 &lt;b&gt;US inflation:&lt;/b&gt; July CPI is the swing factor — with the Fed already flagging oil pass-through, a hot print revives hike pricing.&lt;br&gt;&lt;i&gt;Bias: fade the bounce below 98.36 resistance; back to the 97.33 line.&lt;/i&gt;</t>
+          <t>&lt;b&gt;Week 2 — Sustained Volatility&lt;/b&gt;&lt;br&gt;💥 &lt;b&gt;War:&lt;/b&gt; Continued regional instability keeps oil prices elevated, preventing a quick recovery and maintaining downward pressure on bond prices.&lt;br&gt;🇺🇸 &lt;b&gt;USA:&lt;/b&gt; US geopolitical actions remain the primary driver, overshadowing other economic factors.</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>46234</v>
+        <v>46265.04166666666</v>
       </c>
       <c r="I15" t="n">
-        <v>97.18000000000001</v>
+        <v>95.37</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>superseded by 2026-08-05 re-anchor (drift +1.72, ceasefire signed Aug 2, rally through 98.36)</t>
+          <t>superseded by 2026-08-31 re-anchor (user instruction: "run it again, got fresh data, focus on Iran war and FED expectations")</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46255</v>
+        <v>46290</v>
       </c>
       <c r="B16" t="n">
-        <v>97.3</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="C16" t="n">
-        <v>97.8</v>
+        <v>95.55</v>
       </c>
       <c r="D16" t="n">
-        <v>96.3</v>
+        <v>95.25</v>
       </c>
       <c r="E16" t="n">
-        <v>96.7</v>
+        <v>95.45</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>🇪🇺</t>
+          <t>🇮🇹</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Week 3 — Fade into the September central-bank gauntlet&lt;/b&gt;&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; the truce lapses or frays; Houthi blockade threat on Saudi opens a second front.&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; markets price the 10 Sept projection meeting, where another hike is live — and the Fed is already hawkish.&lt;br&gt;&lt;i&gt;Bias: bearish — 97.33 gives way again, first test of the 96.60 YTD low.&lt;/i&gt;</t>
+          <t>&lt;b&gt;Week 3 — Local Resilience Test&lt;/b&gt;&lt;br&gt;🇮🇹 &lt;b&gt;Italy:&lt;/b&gt; Local economic concerns resurface as the global energy shock hits Europe, causing BTPs to struggle to hold gains despite the overall market.</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>46234</v>
+        <v>46265.04166666666</v>
       </c>
       <c r="I16" t="n">
-        <v>97.18000000000001</v>
+        <v>95.37</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>superseded by 2026-08-05 re-anchor (drift +1.72, ceasefire signed Aug 2, rally through 98.36)</t>
+          <t>superseded by 2026-08-31 re-anchor (user instruction: "run it again, got fresh data, focus on Iran war and FED expectations")</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46262</v>
+        <v>46297</v>
       </c>
       <c r="B17" t="n">
-        <v>96.7</v>
+        <v>95.45</v>
       </c>
       <c r="C17" t="n">
-        <v>97.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="D17" t="n">
-        <v>95.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="E17" t="n">
-        <v>96.3</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>🇺🇸</t>
+          <t>💥</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Week 4 — Jackson Hole&lt;/b&gt;&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; Powell at Jackson Hole ahead of the 15-16 Sept FOMC — after the hawkish July statement, oil-inflation framing there can crack the floor.&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; Sept-hike pricing firms in sympathy.&lt;br&gt;&lt;i&gt;Bias: bearish — break of the 96.60 YTD low toward 95.90. Watch: Hormuz transits, Brent above $95.&lt;/i&gt;</t>
+          <t>&lt;b&gt;Week 4 — Deepening Recession Fears&lt;/b&gt;&lt;br&gt;💥 &lt;b&gt;War:&lt;/b&gt; Escalation fears persist as oil volatility deepens, pushing BTPs toward critical support levels and signaling sustained risk premium.</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>46234</v>
+        <v>46265.04166666666</v>
       </c>
       <c r="I17" t="n">
-        <v>97.18000000000001</v>
+        <v>95.37</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>superseded by 2026-08-05 re-anchor (drift +1.72, ceasefire signed Aug 2, rally through 98.36)</t>
+          <t>superseded by 2026-08-31 re-anchor (user instruction: "run it again, got fresh data, focus on Iran war and FED expectations")</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46248</v>
+        <v>46276</v>
       </c>
       <c r="B18" t="n">
-        <v>98.90000000000001</v>
+        <v>95.37</v>
       </c>
       <c r="C18" t="n">
-        <v>99.59999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="D18" t="n">
-        <v>98.2</v>
+        <v>94.84999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>99.05</v>
+        <v>95.05</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>🇺🇸</t>
+          <t>💥</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Week 1 — Truce rally meets US CPI&lt;/b&gt;&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; the signed truce holds through its first week; oil premium keeps bleeding.&lt;br&gt;🇺🇸 &lt;b&gt;US inflation:&lt;/b&gt; July CPI is the test — oil pass-through was the Fed's stated worry, and the first soft print unlocks more upside.&lt;br&gt;&lt;i&gt;Bias: momentum carries, but the 99.40 resistance caps the first attempt.&lt;/i&gt;</t>
+          <t>Week 1 — Conflict shock drives immediate sell-off&lt;br&gt;💥 &lt;b&gt;War:&lt;/b&gt; US striking Iranian targets spikes oil and risk aversion, overwhelming technical levels.&lt;br&gt;💵 &lt;b&gt;Fed:&lt;/b&gt; Focus shifts to immediate global stability; rate hike talk pauses amid geopolitical uncertainty.</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>46239</v>
+        <v>46265.08333333334</v>
       </c>
       <c r="I18" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>The forecast overestimated the bond's strength, likely due to an overly optimistic view on ECB and Fed policies. For the next forecast, it's crucial to closely monitor geopolitical tensions and their immediate impact on markets.</t>
-        </is>
-      </c>
+        <v>95.37</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46255</v>
+        <v>46283</v>
       </c>
       <c r="B19" t="n">
-        <v>99.05</v>
+        <v>95.05</v>
       </c>
       <c r="C19" t="n">
-        <v>99.45</v>
+        <v>95.5</v>
       </c>
       <c r="D19" t="n">
-        <v>98.2</v>
+        <v>94.5</v>
       </c>
       <c r="E19" t="n">
-        <v>98.55</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>🇪🇺</t>
+          <t>💥</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Week 2 — September gauntlet comes into view&lt;/b&gt;&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; hawks keep the 10 Sept hike live despite cheaper oil — pricing firms as the meeting nears.&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; minutes of the hawkish July FOMC re-read badly.&lt;br&gt;&lt;i&gt;Bias: rally stalls under 99.40, fades toward the 97.96 pivot.&lt;/i&gt;</t>
+          <t>Week 2 — Geopolitical risk deepens downward pressure&lt;br&gt;💥 &lt;b&gt;War:&lt;/b&gt; Escalation in the Strait of Hormuz maintains high risk premium, forcing yields higher and prices lower.&lt;br&gt;💵 &lt;b&gt;Fed:&lt;/b&gt; Inflation outlook remains clouded by global supply shocks, keeping rate cuts distant.</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>46239</v>
+        <v>46265.08333333334</v>
       </c>
       <c r="I19" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>superseded by 2026-08-14 re-anchor (week 2026-08-14 missed; anchor drift -1.57; user instruction: "i just got new data, run the whole thing")</t>
-        </is>
-      </c>
+        <v>95.37</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46262</v>
+        <v>46290</v>
       </c>
       <c r="B20" t="n">
-        <v>98.55</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>99</v>
+        <v>95.45</v>
       </c>
       <c r="D20" t="n">
-        <v>97.7</v>
+        <v>94.7</v>
       </c>
       <c r="E20" t="n">
-        <v>98</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>🇺🇸</t>
+          <t>💵</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Week 3 — Jackson Hole&lt;/b&gt;&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; Powell at Jackson Hole ahead of the 15-16 Sept FOMC — with the truce holding, he can't lean on oil, but 'higher for longer' framing still bites.&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; truce renewal talks at the 10-day expiry are the tail risk.&lt;br&gt;&lt;i&gt;Bias: drift back to the 97.96 support — no floor-break call this time.&lt;/i&gt;</t>
+          <t>Week 3 — FED takes center stage amid crisis volatility&lt;br&gt;💵 &lt;b&gt;Fed:&lt;/b&gt; Fed Chair speaks, emphasizing labor market resilience despite global shocks, suggesting a cautious pause in policy.&lt;br&gt;💥 &lt;b&gt;War:&lt;/b&gt; Conflict severity stabilizes slightly as markets digest the policy input, offering minor technical support.</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>46239</v>
+        <v>46265.08333333334</v>
       </c>
       <c r="I20" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>superseded by 2026-08-14 re-anchor (week 2026-08-14 missed; anchor drift -1.57; user instruction: "i just got new data, run the whole thing")</t>
-        </is>
-      </c>
+        <v>95.37</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46269</v>
+        <v>46297</v>
       </c>
       <c r="B21" t="n">
-        <v>98</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="C21" t="n">
-        <v>98.59999999999999</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>97.3</v>
+        <v>94.95</v>
       </c>
       <c r="E21" t="n">
-        <v>97.59999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>🇪🇺</t>
+          <t>💥</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Week 4 — Run-up to the 10 Sept ECB&lt;/b&gt;&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; decision week looms — a second hike is the base case being priced.&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; August payrolls (Fri) set the tone for the Sept FOMC.&lt;br&gt;&lt;i&gt;Bias: heavy into the event risk; 97.96 tested but holds.&lt;/i&gt;</t>
+          <t>Week 4 — Consolidation near ATL, awaiting conflict resolution&lt;br&gt;💥 &lt;b&gt;War:&lt;/b&gt; Market range-bound as the immediate shock absorbs, but the underlying conflict risk keeps support challenged.&lt;br&gt;💵 &lt;b&gt;Fed:&lt;/b&gt; Policy path remains uncertain; bond pricing remains highly sensitive to any further escalation news.</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>46239</v>
+        <v>46265.08333333334</v>
       </c>
       <c r="I21" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>superseded by 2026-08-14 re-anchor (week 2026-08-14 missed; anchor drift -1.57; user instruction: "i just got new data, run the whole thing")</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>46255</v>
-      </c>
-      <c r="B22" t="n">
-        <v>97.33</v>
-      </c>
-      <c r="C22" t="n">
-        <v>98</v>
-      </c>
-      <c r="D22" t="n">
-        <v>97.33</v>
-      </c>
-      <c r="E22" t="n">
-        <v>97.75</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>🇺🇸</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;Week 1 — Truce rally stalls&lt;/b&gt;&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; hot CPI keeps hike risk alive, 3.25%+ forecast...&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; 10 Sept meeting looms, 2.25% hike confirmed...&lt;br&gt;⚠️ &lt;b&gt;US politics:&lt;/b&gt; midterm election risks, Powell testifies...</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>46248</v>
-      </c>
-      <c r="I22" t="n">
-        <v>97.33</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>superseded by 2026-08-14 re-anchor (user instruction: "i just got new data, run the whole thing")</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B23" t="n">
-        <v>97.75</v>
-      </c>
-      <c r="C23" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="D23" t="n">
-        <v>97.75</v>
-      </c>
-      <c r="E23" t="n">
-        <v>98.3</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>🇪🇺</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;Week 2 — ECB hikes, truce relief&lt;/b&gt;&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; 2.25% hike confirmed, 2027+ rate path...&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; hawkish stance, 3.50%+ forecast...&lt;br&gt;⚠️ &lt;b&gt;US politics:&lt;/b&gt; midterm election risks, Powell testifies...</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>46248</v>
-      </c>
-      <c r="I23" t="n">
-        <v>97.33</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>superseded by 2026-08-14 re-anchor (user instruction: "i just got new data, run the whole thing")</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B24" t="n">
-        <v>98.3</v>
-      </c>
-      <c r="C24" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="D24" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="E24" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;Week 3 — Midterm election risk&lt;/b&gt;&lt;br&gt;⚠️ &lt;b&gt;US politics:&lt;/b&gt; midterm election risks, Powell testifies...&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; hawkish stance, 3.50%+ forecast...&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; 2.25% hike confirmed, 2027+ rate path...</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>46248</v>
-      </c>
-      <c r="I24" t="n">
-        <v>97.33</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>superseded by 2026-08-14 re-anchor (user instruction: "i just got new data, run the whole thing")</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>46276</v>
-      </c>
-      <c r="B25" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="C25" t="n">
-        <v>99</v>
-      </c>
-      <c r="D25" t="n">
-        <v>98.45</v>
-      </c>
-      <c r="E25" t="n">
-        <v>98.75</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>🇪🇺</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;Week 4 — ECB meeting, ceasefire risk&lt;/b&gt;&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; 10 Sept meeting, 2.25%+ hike likely...&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; hawkish stance, 3.50%+ forecast...&lt;br&gt;⚠️ &lt;b&gt;US politics:&lt;/b&gt; midterm election risks, Powell testifies...&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; ceasefire risk, oil prices stabilize...</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>46248</v>
-      </c>
-      <c r="I25" t="n">
-        <v>97.33</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>superseded by 2026-08-14 re-anchor (user instruction: "i just got new data, run the whole thing")</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>46255</v>
-      </c>
-      <c r="B26" t="n">
-        <v>97.33</v>
-      </c>
-      <c r="C26" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="D26" t="n">
-        <v>96.8</v>
-      </c>
-      <c r="E26" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>🇮🇹</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;Week 1 — Truce rally stalls&lt;/b&gt;&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; hot CPI keeps hike risk alive, selloffs target 97.91 support.&lt;br&gt;🇮🇹 &lt;b&gt;Italy:&lt;/b&gt; budget deficit fears pressure BTP as ECB holds rates.</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>46248.04166666666</v>
-      </c>
-      <c r="I26" t="n">
-        <v>97.33</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>PROVISIONAL MISS (week not finished): The forecast missed due to an unexpected escalation in the Israel-Iran conflict, triggering a sharper sell-off than modeled. The war's intensification overwhelmed technical factors, breaking support at 97.91 and driving price below 95.89. Lesson: Geopolitical volatility now dominates over central bank cycles, requiring tighter risk premiums and lower high/low projections in volatile environments.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B27" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="C27" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="D27" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="E27" t="n">
-        <v>97</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>🇪🇺</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;Week 2 — ECB hawkishness dominates&lt;/b&gt;&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; rate hike speculation intensifies ahead of Sept 10 meeting.&lt;br&gt;⚠️ &lt;b&gt;Global:&lt;/b&gt; Iran escalates tensions, but ceasefire limits volatility.</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>46248.04166666666</v>
-      </c>
-      <c r="I27" t="n">
-        <v>97.33</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>superseded by 2026-08-18 re-anchor (week 2026-08-21 missed; anchor drift -1.33; user instruction: "i just got new data, run all, because the last predictions you made were too optimistic, the war is getting real bad and price is dropping faster than you expected")</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B28" t="n">
-        <v>97</v>
-      </c>
-      <c r="C28" t="n">
-        <v>98</v>
-      </c>
-      <c r="D28" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="E28" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>🇪🇺</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;Week 3 — ECB meeting fallout&lt;/b&gt;&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; 2.25% rate hike confirmed, BTP crashes to 96.60 ATL.&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; dovish pivot weakens bond rally.</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>46248.04166666666</v>
-      </c>
-      <c r="I28" t="n">
-        <v>97.33</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>superseded by 2026-08-18 re-anchor (week 2026-08-21 missed; anchor drift -1.33; user instruction: "i just got new data, run all, because the last predictions you made were too optimistic, the war is getting real bad and price is dropping faster than you expected")</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>46276</v>
-      </c>
-      <c r="B29" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="C29" t="n">
-        <v>98.3</v>
-      </c>
-      <c r="D29" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="E29" t="n">
-        <v>97</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>🇪🇺</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;Week 4 — Volatility ahead of Sept 10&lt;/b&gt;&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; inflation data sparks rate hike speculation.&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; Powell hints at pause, but BTP struggles above 97.91.</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>46248.04166666666</v>
-      </c>
-      <c r="I29" t="n">
-        <v>97.33</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>superseded by 2026-08-18 re-anchor (week 2026-08-21 missed; anchor drift -1.33; user instruction: "i just got new data, run all, because the last predictions you made were too optimistic, the war is getting real bad and price is dropping faster than you expected")</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B30" t="n">
-        <v>96</v>
-      </c>
-      <c r="C30" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="D30" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="E30" t="n">
-        <v>95.89</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>🇮🇷</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;Week 1 — Truce rally stalls&lt;/b&gt;&lt;br&gt;🇮🇷 &lt;b&gt;War escalation:&lt;/b&gt; intensified strikes in Hormuz disrupt global supply chains, crushing bond prices...&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; inflation sticks above 3.0% despite ceasefire, keeping rate hike risks alive...</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>46252</v>
-      </c>
-      <c r="I30" t="n">
-        <v>96</v>
-      </c>
-      <c r="J30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B31" t="n">
-        <v>95.89</v>
-      </c>
-      <c r="C31" t="n">
-        <v>96.3</v>
-      </c>
-      <c r="D31" t="n">
-        <v>95.89</v>
-      </c>
-      <c r="E31" t="n">
-        <v>96</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;Week 2 — Volatile ceasefire tug-of-war&lt;/b&gt;&lt;br&gt;⚠️ &lt;b&gt;Geopolitical uncertainty:&lt;/b&gt; conflicting ceasefire violations trigger stop-loss selling...&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; signals rate pause but warns of inflation risks, adding volatility...</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>46252</v>
-      </c>
-      <c r="I31" t="n">
-        <v>96</v>
-      </c>
-      <c r="J31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>46276</v>
-      </c>
-      <c r="B32" t="n">
-        <v>96</v>
-      </c>
-      <c r="C32" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="D32" t="n">
-        <v>95.89</v>
-      </c>
-      <c r="E32" t="n">
-        <v>96.2</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>🇪🇺</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;Week 3 — ECB meeting anxiety&lt;/b&gt;&lt;br&gt;🇪🇺 &lt;b&gt;ECB policy:&lt;/b&gt; hints at potential 25-bp hike in September, spooking bond buyers...&lt;br&gt;🇮🇹 &lt;b&gt;Italy:&lt;/b&gt; fiscal deficit fears resurface as market prices fall below 97.00...</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>46252</v>
-      </c>
-      <c r="I32" t="n">
-        <v>96</v>
-      </c>
-      <c r="J32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>46283</v>
-      </c>
-      <c r="B33" t="n">
-        <v>96.2</v>
-      </c>
-      <c r="C33" t="n">
-        <v>96.7</v>
-      </c>
-      <c r="D33" t="n">
-        <v>95.89</v>
-      </c>
-      <c r="E33" t="n">
-        <v>95.90000000000001</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>🇪🇺</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;Week 4 — ECB decision day&lt;/b&gt;&lt;br&gt;🇪🇺 &lt;b&gt;Rate decision:&lt;/b&gt; 25-bp hike announced, sending BTP to 95.90 as yields surge...&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; maintains hawkish stance, reinforcing bond market selloff...</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>46252</v>
-      </c>
-      <c r="I33" t="n">
-        <v>96</v>
-      </c>
-      <c r="J33" t="inlineStr"/>
+        <v>95.37</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BONDchart/forecast.xlsx
+++ b/BONDchart/forecast.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1124,7 +1124,11 @@
       <c r="I18" t="n">
         <v>95.37</v>
       </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>superseded by 2026-09-01 re-anchor (user instruction: "run it again, got fresh data, focus on Iran war and FED expectations")</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1158,7 +1162,11 @@
       <c r="I19" t="n">
         <v>95.37</v>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>superseded by 2026-09-01 re-anchor (user instruction: "run it again, got fresh data, focus on Iran war and FED expectations")</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1192,7 +1200,11 @@
       <c r="I20" t="n">
         <v>95.37</v>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>superseded by 2026-09-01 re-anchor (user instruction: "run it again, got fresh data, focus on Iran war and FED expectations")</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1226,7 +1238,1059 @@
       <c r="I21" t="n">
         <v>95.37</v>
       </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>superseded by 2026-09-01 re-anchor (user instruction: "run it again, got fresh data, focus on Iran war and FED expectations")</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B22" t="n">
+        <v>95.36</v>
+      </c>
+      <c r="C22" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="D22" t="n">
+        <v>94.75</v>
+      </c>
+      <c r="E22" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>💥</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 1 — Conflict shock drives initial sell-off&lt;/b&gt;&lt;br&gt;💥 &lt;b&gt;War:&lt;/b&gt; Escalation in Hormuz spikes oil prices, creating immediate downside pressure on bonds.&lt;br&gt;💵 &lt;b&gt;Fed:&lt;/b&gt; Increased energy costs heighten fears of a Fed rate hike, overriding technical support.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I22" t="n">
+        <v>95.36</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>superseded by 2026-09-04 re-anchor (user instruction: "run it again, got fresh data, focus on Iran war and FED expectations, inflation")</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B23" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="C23" t="n">
+        <v>95.45</v>
+      </c>
+      <c r="D23" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="E23" t="n">
+        <v>94.65000000000001</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>💵</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 2 — Inflation fears dominate&lt;/b&gt;&lt;br&gt;💵 &lt;b&gt;Fed:&lt;/b&gt; Market focuses on persistent inflation stemming from oil spikes, pushing rate hike expectations higher.&lt;br&gt;💥 &lt;b&gt;War:&lt;/b&gt; Conflict remains the underlying risk, keeping the bond range constrained near structural support.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I23" t="n">
+        <v>95.36</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>superseded by 2026-09-04 re-anchor (user instruction: "run it again, got fresh data, focus on Iran war and FED expectations, inflation")</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B24" t="n">
+        <v>94.65000000000001</v>
+      </c>
+      <c r="C24" t="n">
+        <v>95.05</v>
+      </c>
+      <c r="D24" t="n">
+        <v>94.15000000000001</v>
+      </c>
+      <c r="E24" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 3 — Macro data confirms stress&lt;/b&gt;&lt;br&gt;⚠️ &lt;b&gt;Data:&lt;/b&gt; Weak global growth data, coupled with energy shock, confirms recession fears and rate hike probability.&lt;br&gt;💥 &lt;b&gt;War:&lt;/b&gt; Geopolitical instability keeps the risk premium elevated, limiting any bounce back toward 95.00.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I24" t="n">
+        <v>95.36</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>superseded by 2026-09-04 re-anchor (user instruction: "run it again, got fresh data, focus on Iran war and FED expectations, inflation")</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B25" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="C25" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="D25" t="n">
+        <v>93.7</v>
+      </c>
+      <c r="E25" t="n">
+        <v>94.05</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>💥</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 4 — Structural risk persists&lt;/b&gt;&lt;br&gt;💥 &lt;b&gt;War:&lt;/b&gt; The conflict risk remains the primary driver, forcing bonds lower despite potential minor data relief.&lt;br&gt;💵 &lt;b&gt;Fed:&lt;/b&gt; Rate cut expectations are severely hampered by the immediate energy and inflation shocks.</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I25" t="n">
+        <v>95.36</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>superseded by 2026-09-04 re-anchor (user instruction: "run it again, got fresh data, focus on Iran war and FED expectations, inflation")</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B26" t="n">
+        <v>95.31</v>
+      </c>
+      <c r="C26" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="D26" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>94.55</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>💥</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 1 — Geopolitical Shock Deepens&lt;/b&gt;&lt;br&gt;🇷🇺 &lt;b&gt;Russia:&lt;/b&gt; Public admission of supplying Iran escalates regional tensions, pressuring bond prices.&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; Receives critical military support, heightening war risk premiums.&lt;br&gt;⚠️ &lt;b&gt;Macro:&lt;/b&gt; Inflation concerns are overshadowed by immediate conflict risk, leading to heavy selling.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>46269</v>
+      </c>
+      <c r="I26" t="n">
+        <v>95.31</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>superseded by 2026-09-04 re-anchor (user instruction: "run it again, got fresh data, focus on Iran war and FED expectations, inflation")</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B27" t="n">
+        <v>94.55</v>
+      </c>
+      <c r="C27" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="D27" t="n">
+        <v>94.05</v>
+      </c>
+      <c r="E27" t="n">
+        <v>94.84999999999999</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 2 — Inflation Data Provides Temporary Bounce&lt;/b&gt;&lt;br&gt;⚠️ &lt;b&gt;Macro:&lt;/b&gt; Mixed inflation data (CPI/PPI) suggests softening price pressures, providing temporary technical support.&lt;br&gt;💵 &lt;b&gt;Fed:&lt;/b&gt; Markets digest the inflation data, slightly boosting rate cut expectations.&lt;br&gt;💥 &lt;b&gt;War Risk:&lt;/b&gt; Geopolitical risks remain elevated, capping the rally and maintaining downward pressure.</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>46269</v>
+      </c>
+      <c r="I27" t="n">
+        <v>95.31</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>superseded by 2026-09-04 re-anchor (user instruction: "run it again, got fresh data, focus on Iran war and FED expectations, inflation")</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B28" t="n">
+        <v>94.84999999999999</v>
+      </c>
+      <c r="C28" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="D28" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="E28" t="n">
+        <v>95.15000000000001</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>💵</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 3 — FED Focus Dominates Rate Expectations&lt;/b&gt;&lt;br&gt;💵 &lt;b&gt;Fed:&lt;/b&gt; Focus shifts entirely to future rate paths; bond rally driven by dovish Fed signaling.&lt;br&gt;⚠️ &lt;b&gt;Inflation:&lt;/b&gt; Inflation expectations stabilize, allowing yields to fall.&lt;br&gt;💥 &lt;b&gt;War Risk:&lt;/b&gt; Despite rate optimism, ongoing Russia-Iran tensions prevent a clean breakout above key resistance.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>46269</v>
+      </c>
+      <c r="I28" t="n">
+        <v>95.31</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>superseded by 2026-09-04 re-anchor (user instruction: "run it again, got fresh data, focus on Iran war and FED expectations, inflation")</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B29" t="n">
+        <v>95.15000000000001</v>
+      </c>
+      <c r="C29" t="n">
+        <v>95.34999999999999</v>
+      </c>
+      <c r="D29" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="E29" t="n">
+        <v>94.95</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>💥</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 4 — Geopolitical Risk Reasserts Dominance&lt;/b&gt;&lt;br&gt;💥 &lt;b&gt;War Risk:&lt;/b&gt; The persistent Russia-Iran conflict dominates the narrative, overriding rate expectations and technical support.&lt;br&gt;💵 &lt;b&gt;Fed:&lt;/b&gt; Rate expectations are revisited downwards as geopolitical uncertainty increases.&lt;br&gt;⚠️ &lt;b&gt;Macro:&lt;/b&gt; Inflation data is viewed through a war lens, leading to caution and consolidation near prior support.</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>46269</v>
+      </c>
+      <c r="I29" t="n">
+        <v>95.31</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>superseded by 2026-09-04 re-anchor (user instruction: "run it again, got fresh data, focus on Iran war and FED expectations, inflation")</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B30" t="n">
+        <v>95.31</v>
+      </c>
+      <c r="C30" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="D30" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="E30" t="n">
+        <v>95</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>💥</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 1 — Geopolitical shock dampens rally&lt;/b&gt;&lt;br&gt;💥 &lt;b&gt;War:&lt;/b&gt; Russia supplying Iran military equipment creates immediate risk premium, pushing BTPs lower despite initial consolidation attempts.</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>46269.04166666666</v>
+      </c>
+      <c r="I30" t="n">
+        <v>95.31</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>superseded by 2026-09-04 re-anchor (user instruction: "run it again, got fresh data, focus on Iran war and FED expectations, inflation")</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B31" t="n">
+        <v>95</v>
+      </c>
+      <c r="C31" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="D31" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="E31" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 2 — Inflation concern weighs on bonds&lt;/b&gt;&lt;br&gt;⚠️ &lt;b&gt;Macro Data:&lt;/b&gt; Stronger-than-expected inflation data keeps rate cut hopes muted, causing a slight dip but failing to break key support.</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>46269.04166666666</v>
+      </c>
+      <c r="I31" t="n">
+        <v>95.31</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>superseded by 2026-09-04 re-anchor (user instruction: "run it again, got fresh data, focus on Iran war and FED expectations, inflation")</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B32" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="C32" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="D32" t="n">
+        <v>95</v>
+      </c>
+      <c r="E32" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>💵</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 3 — Fed focus provides temporary lift&lt;/b&gt;&lt;br&gt;💵 &lt;b&gt;FED:&lt;/b&gt; Dovish commentary from Fed officials temporarily outweighs inflation fears, providing a technical bounce and testing higher resistance.</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>46269.04166666666</v>
+      </c>
+      <c r="I32" t="n">
+        <v>95.31</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>superseded by 2026-09-04 re-anchor (user instruction: "run it again, got fresh data, focus on Iran war and FED expectations, inflation")</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B33" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="C33" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="D33" t="n">
+        <v>94.95</v>
+      </c>
+      <c r="E33" t="n">
+        <v>95.15000000000001</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>💥</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 4 — Geopolitical overhang limits upside&lt;/b&gt;&lt;br&gt;💥 &lt;b&gt;War:&lt;/b&gt; Underlying risk from the Russia-Iran axis keeps selling pressure present, trapping the price range near the 95.00 support level.</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>46269.04166666666</v>
+      </c>
+      <c r="I33" t="n">
+        <v>95.31</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>superseded by 2026-09-04 re-anchor (user instruction: "run it again, got fresh data, focus on Iran war and FED expectations, inflation")</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B34" t="n">
+        <v>95.31</v>
+      </c>
+      <c r="C34" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="D34" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="E34" t="n">
+        <v>95</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>💥</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 1 — Geopolitical Shock Absorbs Gains&lt;/b&gt;&lt;br&gt;💥 &lt;b&gt;War:&lt;/b&gt; Escalating military cooperation between Russia and Iran sends shockwaves through global risk sentiment, pressuring bond prices.&lt;br&gt;⚠️ &lt;b&gt;Inflation:&lt;/b&gt; Market focus remains on inflation data, but geopolitical risk takes priority, leading to a sell-off despite mixed macro signals.</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>46269.08333333334</v>
+      </c>
+      <c r="I34" t="n">
+        <v>95.31</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>PROVISIONAL MISS (week not finished): The forecast missed due to a sharp, unexpected downward move driven by a global bond selloff, which was confirmed by the macro briefing and high US yields. The actual low (94.05) significantly exceeded the predicted range, indicating strong selling pressure and momentum not accounted for. Future forecasts must incorporate a higher weighting on US bond market stress and global rate movements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B35" t="n">
+        <v>95</v>
+      </c>
+      <c r="C35" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="D35" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="E35" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 2 — Inflation Data Holds the Line&lt;/b&gt;&lt;br&gt;⚠️ &lt;b&gt;Inflation:&lt;/b&gt; US inflation data comes in hotter than anticipated, raising concerns about persistent price pressures and delaying rate cut expectations.&lt;br&gt;💵 &lt;b&gt;Fed:&lt;/b&gt; The FED signals a more cautious, data-dependent stance, providing some technical support to the BTPs despite the conflict risk.</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>46269.08333333334</v>
+      </c>
+      <c r="I35" t="n">
+        <v>95.31</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>superseded by 2026-09-09 re-anchor (week 2026-09-11 missed; anchor drift -1.11; user instruction: "run it again, got fresh data, focus on US bond crisis")</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B36" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="C36" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="D36" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="E36" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>🇮🇷</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 3 — Conflict Risk Persists&lt;/b&gt;&lt;br&gt;🇮🇷 &lt;b&gt;Iran/Conflict:&lt;/b&gt; The visible military entanglement between Russia and Iran keeps elevated risk premiums in place, capping any significant rally.&lt;br&gt;💵 &lt;b&gt;Fed:&lt;/b&gt; Rate expectations are tempered by the conflict, forcing the FED to remain non-committal, keeping yields sticky.</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>46269.08333333334</v>
+      </c>
+      <c r="I36" t="n">
+        <v>95.31</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>superseded by 2026-09-09 re-anchor (week 2026-09-11 missed; anchor drift -1.11; user instruction: "run it again, got fresh data, focus on US bond crisis")</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B37" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="C37" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="D37" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="E37" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>💵</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 4 — Dovish Pivot Support&lt;/b&gt;&lt;br&gt;💵 &lt;b&gt;Fed:&lt;/b&gt; Market anticipation builds for a dovish shift in FED tone, suggesting rate cuts are more likely than previously priced.&lt;br&gt;⚠️ &lt;b&gt;Inflation:&lt;/b&gt; While inflation remains a concern, the potential for a policy pivot offers a technical floor, allowing the BTPs to stabilize above key support levels.</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>46269.08333333334</v>
+      </c>
+      <c r="I37" t="n">
+        <v>95.31</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>superseded by 2026-09-09 re-anchor (week 2026-09-11 missed; anchor drift -1.11; user instruction: "run it again, got fresh data, focus on US bond crisis")</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B38" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="C38" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="D38" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="E38" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>🇺🇸</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 1 — US Yields Drag BTP Lower&lt;/b&gt;&lt;br&gt;🇺🇸 &lt;b&gt;US:&lt;/b&gt; High US 10-year yields (4.857%) fuel global bond selloff, pressuring European debt.&lt;br&gt;⚠️ &lt;b&gt;Macro:&lt;/b&gt; Bond selloff confirms global risk aversion, targeting lower support levels.</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="I38" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>superseded by 2026-09-11 re-anchor (anchor drift -0.61; user instruction: "run it again, got fresh data")</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B39" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="C39" t="n">
+        <v>94</v>
+      </c>
+      <c r="D39" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>93.34999999999999</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>🇺🇸</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 2 — Selloff Continues Below ATL&lt;/b&gt;&lt;br&gt;🇺🇸 &lt;b&gt;US:&lt;/b&gt; Persistent US bond stress keeps downward pressure on Italian rates.&lt;br&gt;⚠️ &lt;b&gt;Macro:&lt;/b&gt; Global bond selloff persists, testing psychological support and key technical levels.</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="I39" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>superseded by 2026-09-11 re-anchor (anchor drift -0.61; user instruction: "run it again, got fresh data")</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B40" t="n">
+        <v>93.34999999999999</v>
+      </c>
+      <c r="C40" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="D40" t="n">
+        <v>93</v>
+      </c>
+      <c r="E40" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 3 — Oil Price &amp; Stress Test Support&lt;/b&gt;&lt;br&gt;⚠️ &lt;b&gt;Macro:&lt;/b&gt; $101 oil and US yield concerns create volatility, but BTP finds temporary support near 93.50.&lt;br&gt;🇺🇸 &lt;b&gt;US:&lt;/b&gt; US bond market remains the primary source of downward risk.</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="I40" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>superseded by 2026-09-11 re-anchor (anchor drift -0.61; user instruction: "run it again, got fresh data")</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B41" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="C41" t="n">
+        <v>94</v>
+      </c>
+      <c r="D41" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="E41" t="n">
+        <v>93.65000000000001</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>🇺🇸</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 4 — Consolidation Amid US Uncertainty&lt;/b&gt;&lt;br&gt;🇺🇸 &lt;b&gt;US:&lt;/b&gt; US bond crisis narrative keeps risk elevated, limiting upside for Italian bonds.&lt;br&gt;⚠️ &lt;b&gt;Macro:&lt;/b&gt; BTP consolidates in a tight range, digesting the impact of global bond selloff driven by US rates.</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="I41" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>superseded by 2026-09-11 re-anchor (anchor drift -0.61; user instruction: "run it again, got fresh data")</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B42" t="n">
+        <v>93.59</v>
+      </c>
+      <c r="C42" t="n">
+        <v>94.25</v>
+      </c>
+      <c r="D42" t="n">
+        <v>92.84999999999999</v>
+      </c>
+      <c r="E42" t="n">
+        <v>93.05</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 1 — Yield Stress Persists&lt;/b&gt;&lt;br&gt;⚠️ &lt;b&gt;Macro Data:&lt;/b&gt; Global bond selloffs continue despite energy shocks, keeping US 10-year yields near 5.00% and pressuring BTPs below 93.59.</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="I42" t="n">
+        <v>93.59</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>The forecast underestimated the immediate buying support, as the bond price rejected the lower range and closed strongly at 93.61, confirming a bounce. The market appears to have found a firmer floor, potentially reacting to the yield retreat noted in the macro briefing. Future forecasts must account for this immediate resilience and the strength of the support level established at 93.61.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B43" t="n">
+        <v>93.05</v>
+      </c>
+      <c r="C43" t="n">
+        <v>93.7</v>
+      </c>
+      <c r="D43" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="E43" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>🇺🇸</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 2 — US Yields Anchor Selloff&lt;/b&gt;&lt;br&gt;🇺🇸 &lt;b&gt;USA:&lt;/b&gt; High US yields remain sticky, fueled by energy price shocks (WTI $100+), limiting short-term upside for European bonds.</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="I43" t="n">
+        <v>93.59</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>superseded by 2026-09-18 re-anchor (week 2026-09-18 missed; user instruction: "run it again, got fresh data, focus on the FED and OIL")</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B44" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="C44" t="n">
+        <v>93.34999999999999</v>
+      </c>
+      <c r="D44" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="E44" t="n">
+        <v>92.45</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 3 — Energy Shock Drives Selling&lt;/b&gt;&lt;br&gt;⚠️ &lt;b&gt;Macro Data:&lt;/b&gt; Surging oil prices ($108+) intensify global risk perception, driving bond selloffs and breaking support near 92.90.</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="I44" t="n">
+        <v>93.59</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>superseded by 2026-09-18 re-anchor (week 2026-09-18 missed; user instruction: "run it again, got fresh data, focus on the FED and OIL")</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B45" t="n">
+        <v>92.45</v>
+      </c>
+      <c r="C45" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="D45" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="E45" t="n">
+        <v>92.15000000000001</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 4 — Testing Support Levels&lt;/b&gt;&lt;br&gt;⚠️ &lt;b&gt;Macro Data:&lt;/b&gt; Continued macro uncertainty keeps selling pressure high, challenging the 92.20 support and pushing prices toward 92.00.</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="I45" t="n">
+        <v>93.59</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>superseded by 2026-09-18 re-anchor (week 2026-09-18 missed; user instruction: "run it again, got fresh data, focus on the FED and OIL")</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B46" t="n">
+        <v>93.61</v>
+      </c>
+      <c r="C46" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="D46" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="E46" t="n">
+        <v>93.15000000000001</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>💵</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 1 — Fed Hikes &amp; Oil Concerns&lt;/b&gt;&lt;br&gt;💵 &lt;b&gt;Fed:&lt;/b&gt; Rate hike expectations dominate, pressuring bond prices despite initial yield retreat.&lt;br&gt;⚠️ &lt;b&gt;Oil:&lt;/b&gt; Volatile oil prices create persistent inflation fears, limiting upside for BTPs.</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="I46" t="n">
+        <v>93.61</v>
+      </c>
+      <c r="J46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B47" t="n">
+        <v>93.15000000000001</v>
+      </c>
+      <c r="C47" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="D47" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="E47" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 2 — Oil Price Volatility Tests Support&lt;/b&gt;&lt;br&gt;⚠️ &lt;b&gt;Oil:&lt;/b&gt; Global oil price shocks weigh heavily on European growth forecasts, pushing yields higher.&lt;br&gt;💵 &lt;b&gt;Fed:&lt;/b&gt; Market remains focused on the Fed's hawkish stance, absorbing oil-related macro data.</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="I47" t="n">
+        <v>93.61</v>
+      </c>
+      <c r="J47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B48" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="C48" t="n">
+        <v>93.05</v>
+      </c>
+      <c r="D48" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="E48" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>💵</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 3 — Rate Hike Impact Constrains Rally&lt;/b&gt;&lt;br&gt;💵 &lt;b&gt;Fed:&lt;/b&gt; Continued hawkish signals from the Fed keep rate hike risk alive, capping any significant bond rally.&lt;br&gt;⚠️ &lt;b&gt;Oil:&lt;/b&gt; Inflationary pressures from oil keep the market cautious, preventing a decisive reversal.</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="I48" t="n">
+        <v>93.61</v>
+      </c>
+      <c r="J48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B49" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="C49" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="D49" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="E49" t="n">
+        <v>92.05</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>💵</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 4 — Bearish Drift on Policy Uncertainty&lt;/b&gt;&lt;br&gt;💵 &lt;b&gt;Fed:&lt;/b&gt; The focus remains squarely on the Fed's tightening cycle, leading to a downward drift in bond prices.&lt;br&gt;⚠️ &lt;b&gt;Oil:&lt;/b&gt; Weakening global demand, exacerbated by oil price uncertainty, reinforces the bearish technical setup.</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="I49" t="n">
+        <v>93.61</v>
+      </c>
+      <c r="J49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BONDchart/forecast.xlsx
+++ b/BONDchart/forecast.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2188,7 +2188,11 @@
       <c r="I46" t="n">
         <v>93.61</v>
       </c>
-      <c r="J46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>The forecast underestimated the downside risk, predicting a range centered around 93.15, while the actual candle saw a significant drop to 92.63, driven by the geopolitical shock of Trump rejecting Iran's deal. The lesson is that major, unexpected geopolitical events can override technical resistance and support levels, requiring a wider downside buffer in future forecasts.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -2222,7 +2226,11 @@
       <c r="I47" t="n">
         <v>93.61</v>
       </c>
-      <c r="J47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>PROVISIONAL MISS (week not finished): The forecast significantly overshot the actual market movement, missing the sharp decline to 91.75, likely due to the unexpected bearish impact of Trump rejecting the Iran deal. Future forecasts must account for immediate, sharp drops triggered by geopolitical shocks, as these events can override technical support and cause rapid price deterioration.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -2256,7 +2264,11 @@
       <c r="I48" t="n">
         <v>93.61</v>
       </c>
-      <c r="J48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>superseded by 2026-09-28 re-anchor (week 2026-09-25 missed; week 2026-10-02 missed; anchor drift -1.86; user instruction: "run it again, got fresh data")</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -2290,7 +2302,299 @@
       <c r="I49" t="n">
         <v>93.61</v>
       </c>
-      <c r="J49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>superseded by 2026-09-28 re-anchor (week 2026-09-25 missed; week 2026-10-02 missed; anchor drift -1.86; user instruction: "run it again, got fresh data")</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="C50" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="D50" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="E50" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>🇮🇷</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 1 — Geopolitical Shock Absorbs&lt;/b&gt;&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; Trump's rejection of the deal drives immediate yield spikes, pushing prices down sharply toward the ATL.&lt;br&gt;🇺🇸 &lt;b&gt;USA:&lt;/b&gt; Rising 30-year yields (5.58%) and oil ($109) confirm significant downside pressure on sovereign debt markets.</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="I50" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>superseded by 2026-09-28 re-anchor (user instruction: "run it again, got fresh data, dont underestimate how lower the bond can go, your predictions tend to be higher than reality")</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="C51" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="D51" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="E51" t="n">
+        <v>90.95</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>🇺🇸</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 2 — Yield Stress Deepens&lt;/b&gt;&lt;br&gt;🇺🇸 &lt;b&gt;USA:&lt;/b&gt; Persistent US policy uncertainty and high yields keep selling pressure active, testing critical support levels below the previous weekly low.&lt;br&gt;⚠️ &lt;b&gt;Macro:&lt;/b&gt; Market focus remains on global bond stress and rate hike expectations, limiting upward bounce.</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="I51" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>superseded by 2026-09-28 re-anchor (user instruction: "run it again, got fresh data, dont underestimate how lower the bond can go, your predictions tend to be higher than reality")</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B52" t="n">
+        <v>90.95</v>
+      </c>
+      <c r="C52" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="D52" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="E52" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 3 — Risk-Off Bounce Attempt&lt;/b&gt;&lt;br&gt;⚠️ &lt;b&gt;Macro:&lt;/b&gt; Extreme discount levels draw in risk-off capital, providing temporary buying support, but the underlying macro overhang remains a significant headwind.&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; The ECB monitors the global stress, signaling readiness to intervene if the bond market stability deteriorates further.</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="I52" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>superseded by 2026-09-28 re-anchor (user instruction: "run it again, got fresh data, dont underestimate how lower the bond can go, your predictions tend to be higher than reality")</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B53" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="C53" t="n">
+        <v>91.34999999999999</v>
+      </c>
+      <c r="D53" t="n">
+        <v>90.95</v>
+      </c>
+      <c r="E53" t="n">
+        <v>91</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>🇪🇺</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 4 — Range-Bound Consolidation&lt;/b&gt;&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; The ECB attempts to anchor expectations, leading to tight consolidation as the market digests the geopolitical fallout.&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; The price finds a temporary equilibrium range, awaiting clarity on the geopolitical situation before any major directional move can resume.</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="I53" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>superseded by 2026-09-28 re-anchor (user instruction: "run it again, got fresh data, dont underestimate how lower the bond can go, your predictions tend to be higher than reality")</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B54" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="C54" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="D54" t="n">
+        <v>91</v>
+      </c>
+      <c r="E54" t="n">
+        <v>91</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>🇮🇷</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 1 — Initial Geopolitical Shock Absorbed&lt;/b&gt;&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; Market digests the initial offer/rejection cycle, leading to a dip as uncertainty persists, but immediate support holds around the 91.00 mark.</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>46293.04166666666</v>
+      </c>
+      <c r="I54" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="J54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91</v>
+      </c>
+      <c r="C55" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="D55" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="E55" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>🇮🇷</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 2 — Tensions Deepen&lt;/b&gt;&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; Continued lack of clarity regarding sanctions relief keeps selling pressure elevated, pushing prices lower and testing the immediate psychological support.</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>46293.04166666666</v>
+      </c>
+      <c r="I55" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="J55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B56" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="C56" t="n">
+        <v>91</v>
+      </c>
+      <c r="D56" t="n">
+        <v>89.84999999999999</v>
+      </c>
+      <c r="E56" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>🇮🇷</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 3 — Bearish Momentum Takes Hold&lt;/b&gt;&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; The market reacts to the sustained risk of the deal failing, breaking below key short-term support and accelerating the downward slide.</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>46293.04166666666</v>
+      </c>
+      <c r="I56" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="J56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B57" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="C57" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="D57" t="n">
+        <v>89.15000000000001</v>
+      </c>
+      <c r="E57" t="n">
+        <v>89.25</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>🇮🇷</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 4 — Sustained Downside Risk&lt;/b&gt;&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; Geopolitical risks remain paramount, with selling pressure continuing to test deeper levels, suggesting the market has not yet priced in a stable resolution to the sanctions issue.</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>46293.04166666666</v>
+      </c>
+      <c r="I57" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="J57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BONDchart/forecast.xlsx
+++ b/BONDchart/forecast.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2492,7 +2492,11 @@
       <c r="I54" t="n">
         <v>91.75</v>
       </c>
-      <c r="J54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>superseded by 2026-10-02 re-anchor (user instruction: "run it again, got fresh data, focus on diesel")</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -2526,7 +2530,11 @@
       <c r="I55" t="n">
         <v>91.75</v>
       </c>
-      <c r="J55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>superseded by 2026-10-02 re-anchor (user instruction: "run it again, got fresh data, focus on diesel")</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -2560,7 +2568,11 @@
       <c r="I56" t="n">
         <v>91.75</v>
       </c>
-      <c r="J56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>superseded by 2026-10-02 re-anchor (user instruction: "run it again, got fresh data, focus on diesel")</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -2594,7 +2606,295 @@
       <c r="I57" t="n">
         <v>91.75</v>
       </c>
-      <c r="J57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>superseded by 2026-10-02 re-anchor (user instruction: "run it again, got fresh data, focus on diesel")</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B58" t="n">
+        <v>92</v>
+      </c>
+      <c r="C58" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="D58" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="E58" t="n">
+        <v>91.65000000000001</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 1 — Diesel Supply Shock Begins&lt;/b&gt;&lt;br&gt;⚠️ &lt;b&gt;Energy/Macro:&lt;/b&gt; Global diesel supply fears intensify due to export suspensions from Russia and China, pressuring bond prices lower this week.</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="I58" t="n">
+        <v>92</v>
+      </c>
+      <c r="J58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B59" t="n">
+        <v>91.65000000000001</v>
+      </c>
+      <c r="C59" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="D59" t="n">
+        <v>91</v>
+      </c>
+      <c r="E59" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 2 — EU Reserve Vulnerability&lt;/b&gt;&lt;br&gt;⚠️ &lt;b&gt;Energy/Macro:&lt;/b&gt; Concerns shift to EU energy reserves, amplifying the bearish pressure initiated by the diesel supply risks, keeping the market volatile.</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="I59" t="n">
+        <v>92</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>superseded by 2026-10-09 re-anchor (user instruction: "run it again, got fresh data")</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B60" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="C60" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="D60" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="E60" t="n">
+        <v>91.05</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 3 — Consolidating on Energy Risk&lt;/b&gt;&lt;br&gt;⚠️ &lt;b&gt;Energy/Macro:&lt;/b&gt; Market finds temporary support around 91.00, but the underlying risk from curtailed Russian and Chinese energy exports keeps the macro uncertainty high.</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="I60" t="n">
+        <v>92</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>superseded by 2026-10-09 re-anchor (user instruction: "run it again, got fresh data")</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B61" t="n">
+        <v>91.05</v>
+      </c>
+      <c r="C61" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="D61" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="E61" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 4 — Persistent Geopolitical Discount&lt;/b&gt;&lt;br&gt;⚠️ &lt;b&gt;Energy/Macro:&lt;/b&gt; The threat of sustained diesel supply shortages remains the dominant factor, maintaining a negative risk premium and keeping the bond range constrained below previous highs.</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="I61" t="n">
+        <v>92</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>superseded by 2026-10-09 re-anchor (user instruction: "run it again, got fresh data")</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B62" t="n">
+        <v>91.79000000000001</v>
+      </c>
+      <c r="C62" t="n">
+        <v>93</v>
+      </c>
+      <c r="D62" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="E62" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>🇺🇸</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 1 — Energy Supply Stabilization&lt;/b&gt;&lt;br&gt;🇺🇸 &lt;b&gt;USA:&lt;/b&gt; Easing Russian diesel sanctions provides immediate supply relief, stabilizing energy prices and providing a temporary floor for BTPs.&lt;br&gt;⚠️ &lt;b&gt;Macro:&lt;/b&gt; Initial price bounce reflects commodity flow improvements, overshadowing immediate rate concerns.</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="I62" t="n">
+        <v>91.79000000000001</v>
+      </c>
+      <c r="J62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B63" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="C63" t="n">
+        <v>94</v>
+      </c>
+      <c r="D63" t="n">
+        <v>92</v>
+      </c>
+      <c r="E63" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>🇷🇺</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 2 — Geopolitical Impact Digest&lt;/b&gt;&lt;br&gt;🇷🇺 &lt;b&gt;Russia:&lt;/b&gt; Continued diesel exports are priced in, reducing the immediate yield pressure from energy markets.&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; Focus shifts to inflation path, as energy supply stability moderates the rate of expected rate cuts.</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="I63" t="n">
+        <v>91.79000000000001</v>
+      </c>
+      <c r="J63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B64" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="C64" t="n">
+        <v>95</v>
+      </c>
+      <c r="D64" t="n">
+        <v>93</v>
+      </c>
+      <c r="E64" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 3 — Inflation Expectations Test&lt;/b&gt;&lt;br&gt;⚠️ &lt;b&gt;Macro:&lt;/b&gt; Bond market digests the energy news alongside upcoming US inflation data, suggesting rate cuts are more likely than previously anticipated.&lt;br&gt;🇮🇹 &lt;b&gt;Italy:&lt;/b&gt; BTPs find support from improving global energy supply metrics.</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="I64" t="n">
+        <v>91.79000000000001</v>
+      </c>
+      <c r="J64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>46332</v>
+      </c>
+      <c r="B65" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="C65" t="n">
+        <v>96</v>
+      </c>
+      <c r="D65" t="n">
+        <v>94</v>
+      </c>
+      <c r="E65" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>💵</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Week 4 — Rate Path Confirmation&lt;/b&gt;&lt;br&gt;💵 &lt;b&gt;FED:&lt;/b&gt; Market anticipates clearer dovish signals from the Fed, driven by stable energy prices and moderating inflation outlook.&lt;br&gt;🇺🇸 &lt;b&gt;USA:&lt;/b&gt; Increased focus on the Fed's forward guidance, pushing yields lower and supporting BTPs.</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="I65" t="n">
+        <v>91.79000000000001</v>
+      </c>
+      <c r="J65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
